--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -47281,12 +47281,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -47311,7 +47311,7 @@
       </c>
       <c r="L268" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M268" t="inlineStr">
@@ -47326,75 +47326,94 @@
         <v>1</v>
       </c>
       <c r="R268" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ268" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR268" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT268" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -47421,17 +47440,17 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47456,7 +47475,7 @@
       </c>
       <c r="L269" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M269" t="inlineStr">
@@ -47465,81 +47484,175 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O269" t="n">
-        <v>0</v>
-      </c>
-      <c r="R269" t="n">
-        <v>0</v>
-      </c>
-      <c r="S269" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X269" t="inlineStr">
+        <is>
+          <t>Brucellos</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z269" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB269" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC269" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD269" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE269" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF269" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG269" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH269" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI269" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ269" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK269" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM269" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN269" t="b">
+        <v>1</v>
       </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ269" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR269" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT269" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -47571,12 +47684,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47601,7 +47714,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -47616,7 +47729,7 @@
         <v>1</v>
       </c>
       <c r="R270" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S270" t="inlineStr">
         <is>
@@ -47649,42 +47762,42 @@
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -47746,7 +47859,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -47891,7 +48004,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -48036,7 +48149,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -48181,7 +48294,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -48190,13 +48303,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O274" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R274" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -48296,12 +48409,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -48326,12 +48439,12 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N275" t="n">
@@ -48374,42 +48487,42 @@
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48441,12 +48554,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -48471,22 +48584,22 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R276" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -48519,42 +48632,42 @@
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -48586,12 +48699,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -48638,87 +48751,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U277" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA277" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ277" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR277" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS277" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr"/>
       <c r="AT277" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -48745,217 +48839,526 @@
       </c>
       <c r="E278" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J278" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L278" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N278" t="n">
+        <v>0</v>
+      </c>
+      <c r="O278" t="n">
+        <v>0</v>
+      </c>
+      <c r="R278" t="n">
+        <v>0</v>
+      </c>
+      <c r="S278" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO278" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP278" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR278" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr"/>
+      <c r="AT278" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU278" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV278" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ278" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA278" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB278" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC278" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E279" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J279" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L279" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M279" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N279" t="n">
+        <v>0</v>
+      </c>
+      <c r="O279" t="n">
+        <v>0</v>
+      </c>
+      <c r="R279" t="n">
+        <v>0</v>
+      </c>
+      <c r="S279" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR279" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT279" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU279" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV279" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ279" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA279" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB279" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC279" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E280" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F278" t="inlineStr">
+      <c r="F280" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G278" t="inlineStr">
+      <c r="G280" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I278" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J278" t="inlineStr">
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J280" t="inlineStr">
         <is>
           <t>布鲁氏菌病</t>
         </is>
       </c>
-      <c r="K278" t="inlineStr">
+      <c r="K280" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L278" t="inlineStr">
+      <c r="L280" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M278" t="inlineStr">
+      <c r="M280" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N278" t="n">
-        <v>0</v>
-      </c>
-      <c r="O278" t="n">
-        <v>0</v>
-      </c>
-      <c r="U278" t="inlineStr">
+      <c r="N280" t="n">
+        <v>0</v>
+      </c>
+      <c r="O280" t="n">
+        <v>0</v>
+      </c>
+      <c r="U280" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="V278" t="inlineStr">
+      <c r="V280" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="W278" t="inlineStr">
+      <c r="W280" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X278" t="inlineStr">
+      <c r="X280" t="inlineStr">
         <is>
           <t>Brucellose</t>
         </is>
       </c>
-      <c r="Y278" t="inlineStr">
+      <c r="Y280" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z278" t="inlineStr">
+      <c r="Z280" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA278" t="inlineStr">
+      <c r="AA280" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB278" t="inlineStr">
+      <c r="AB280" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC278" t="inlineStr">
+      <c r="AC280" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD278" t="inlineStr">
+      <c r="AD280" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE278" t="inlineStr">
+      <c r="AE280" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF278" t="inlineStr">
+      <c r="AF280" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG278" t="inlineStr">
+      <c r="AG280" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH278" t="inlineStr">
+      <c r="AH280" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI278" t="inlineStr">
+      <c r="AI280" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ278" t="inlineStr">
+      <c r="AJ280" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK278" t="inlineStr">
+      <c r="AK280" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM278" t="inlineStr">
+      <c r="AM280" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN278" t="b">
+      <c r="AN280" t="b">
         <v>1</v>
       </c>
-      <c r="AO278" t="inlineStr">
+      <c r="AO280" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP278" t="inlineStr">
+      <c r="AP280" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ278" t="inlineStr">
+      <c r="AQ280" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR278" t="inlineStr">
+      <c r="AR280" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS278" t="inlineStr">
+      <c r="AS280" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="AT278" t="n">
+      <c r="AT280" t="n">
         <v>2</v>
       </c>
-      <c r="AU278" t="inlineStr">
+      <c r="AU280" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV278" t="inlineStr">
+      <c r="AV280" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW278" t="inlineStr">
+      <c r="AW280" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX278" t="inlineStr">
+      <c r="AX280" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY278" t="inlineStr">
+      <c r="AY280" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ278" t="inlineStr">
+      <c r="AZ280" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA278" t="inlineStr">
+      <c r="BA280" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB278" t="inlineStr">
+      <c r="BB280" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC278" t="inlineStr">
+      <c r="BC280" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -49077,7 +49480,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>196</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10">
@@ -49087,7 +49490,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="11">
@@ -49107,7 +49510,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="13">
@@ -49139,7 +49542,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43603</v>
+        <v>43604</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -48699,12 +48699,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -48729,12 +48729,12 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N277" t="n">
@@ -48777,42 +48777,42 @@
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48844,12 +48844,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -48922,42 +48922,42 @@
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -48989,12 +48989,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -49041,87 +49041,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U279" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA279" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO279" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP279" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ279" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR279" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS279" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr"/>
       <c r="AT279" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -49148,7 +49129,7 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
@@ -49197,98 +49178,23 @@
       <c r="O280" t="n">
         <v>0</v>
       </c>
+      <c r="R280" t="n">
+        <v>0</v>
+      </c>
+      <c r="S280" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U280" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="V280" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W280" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X280" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y280" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z280" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA280" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB280" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC280" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD280" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE280" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF280" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG280" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH280" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI280" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ280" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK280" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM280" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN280" t="b">
-        <v>1</v>
       </c>
       <c r="AO280" t="inlineStr">
         <is>
@@ -49359,6 +49265,245 @@
         </is>
       </c>
       <c r="BC280" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E281" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J281" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L281" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M281" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N281" t="n">
+        <v>0</v>
+      </c>
+      <c r="O281" t="n">
+        <v>0</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM281" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN281" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO281" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP281" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR281" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT281" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU281" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV281" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ281" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA281" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB281" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC281" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -49480,7 +49625,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>197</v>
+        <v>198</v>
       </c>
     </row>
     <row r="10">
@@ -49490,7 +49635,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -46733,12 +46733,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46772,13 +46772,16 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>1</v>
+        <v>6151</v>
       </c>
       <c r="O265" t="n">
-        <v>1</v>
+        <v>6151</v>
+      </c>
+      <c r="Q265" t="n">
+        <v>0</v>
       </c>
       <c r="R265" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.4353414018633023</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
@@ -46811,42 +46814,42 @@
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -46878,12 +46881,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46917,100 +46920,81 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O266" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R266" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U266" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA266" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO266" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP266" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ266" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR266" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS266" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS266" t="inlineStr"/>
       <c r="AT266" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU266" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -47037,7 +47021,7 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
@@ -47086,98 +47070,23 @@
       <c r="O267" t="n">
         <v>0</v>
       </c>
+      <c r="R267" t="n">
+        <v>0</v>
+      </c>
+      <c r="S267" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U267" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="V267" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W267" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X267" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y267" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z267" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA267" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB267" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC267" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD267" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE267" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF267" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG267" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH267" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI267" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ267" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK267" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM267" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN267" t="b">
-        <v>1</v>
       </c>
       <c r="AO267" t="inlineStr">
         <is>
@@ -47276,17 +47185,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -47320,29 +47229,104 @@
         </is>
       </c>
       <c r="N268" t="n">
+        <v>0</v>
+      </c>
+      <c r="O268" t="n">
+        <v>0</v>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X268" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z268" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB268" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC268" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD268" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE268" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF268" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG268" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH268" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI268" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ268" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK268" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM268" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN268" t="b">
         <v>1</v>
       </c>
-      <c r="O268" t="n">
-        <v>1</v>
-      </c>
-      <c r="R268" t="n">
-        <v>0.009344880428283346</v>
-      </c>
-      <c r="S268" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
-        </is>
-      </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47365,7 +47349,7 @@
       </c>
       <c r="AS268" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT268" t="n">
@@ -47378,42 +47362,42 @@
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -47440,7 +47424,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -47489,98 +47473,23 @@
       <c r="O269" t="n">
         <v>1</v>
       </c>
+      <c r="R269" t="n">
+        <v>0.009344880428283346</v>
+      </c>
+      <c r="S269" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U269" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
         </is>
       </c>
-      <c r="V269" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
-        </is>
-      </c>
-      <c r="W269" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X269" t="inlineStr">
-        <is>
-          <t>Brucellos</t>
-        </is>
-      </c>
-      <c r="Y269" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z269" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA269" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB269" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC269" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD269" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE269" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF269" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG269" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH269" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI269" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ269" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK269" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM269" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN269" t="b">
-        <v>1</v>
       </c>
       <c r="AO269" t="inlineStr">
         <is>
@@ -47679,17 +47588,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47714,7 +47623,7 @@
       </c>
       <c r="L270" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M270" t="inlineStr">
@@ -47728,76 +47637,170 @@
       <c r="O270" t="n">
         <v>1</v>
       </c>
-      <c r="R270" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S270" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X270" t="inlineStr">
+        <is>
+          <t>Brucellos</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z270" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB270" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC270" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD270" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE270" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF270" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG270" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH270" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI270" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ270" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK270" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM270" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN270" t="b">
+        <v>1</v>
       </c>
       <c r="AO270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ270" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR270" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS270" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS270" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT270" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -47859,7 +47862,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -47868,13 +47871,13 @@
         </is>
       </c>
       <c r="N271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R271" t="n">
-        <v>0</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
@@ -47974,12 +47977,12 @@
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -48004,7 +48007,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -48013,13 +48016,13 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O272" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R272" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S272" t="inlineStr">
         <is>
@@ -48052,42 +48055,42 @@
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48119,12 +48122,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -48149,7 +48152,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -48158,13 +48161,13 @@
         </is>
       </c>
       <c r="N273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O273" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R273" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -48197,42 +48200,42 @@
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -48264,12 +48267,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -48294,7 +48297,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -48303,13 +48306,13 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O274" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R274" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
@@ -48342,42 +48345,42 @@
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48409,12 +48412,12 @@
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -48439,7 +48442,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -48448,13 +48451,13 @@
         </is>
       </c>
       <c r="N275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O275" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R275" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S275" t="inlineStr">
         <is>
@@ -48487,42 +48490,42 @@
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -48554,12 +48557,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -48584,7 +48587,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -48593,13 +48596,13 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O276" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="R276" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
@@ -48632,42 +48635,42 @@
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48699,12 +48702,12 @@
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -48729,7 +48732,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -48738,13 +48741,13 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R277" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S277" t="inlineStr">
         <is>
@@ -48777,42 +48780,42 @@
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -48844,12 +48847,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -48874,12 +48877,12 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N278" t="n">
@@ -48922,42 +48925,42 @@
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48989,12 +48992,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -49067,42 +49070,42 @@
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -49134,12 +49137,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -49186,87 +49189,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U280" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA280" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO280" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ280" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR280" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS280" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr"/>
       <c r="AT280" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -49293,7 +49277,7 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -49342,98 +49326,23 @@
       <c r="O281" t="n">
         <v>0</v>
       </c>
+      <c r="R281" t="n">
+        <v>0</v>
+      </c>
+      <c r="S281" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U281" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="V281" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W281" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X281" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y281" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z281" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA281" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB281" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC281" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD281" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE281" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF281" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG281" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH281" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI281" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ281" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK281" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM281" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN281" t="b">
-        <v>1</v>
       </c>
       <c r="AO281" t="inlineStr">
         <is>
@@ -49504,6 +49413,245 @@
         </is>
       </c>
       <c r="BC281" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E282" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X282" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z282" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB282" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC282" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD282" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE282" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF282" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG282" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH282" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI282" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ282" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK282" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM282" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN282" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT282" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -49625,7 +49773,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
     </row>
     <row r="10">
@@ -49635,7 +49783,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="11">
@@ -49687,7 +49835,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>43604</v>
+        <v>49755</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -39968,12 +39968,12 @@
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
@@ -40007,84 +40007,92 @@
         </is>
       </c>
       <c r="N225" t="n">
-        <v>6996</v>
+        <v>0</v>
       </c>
       <c r="O225" t="n">
-        <v>6996</v>
-      </c>
-      <c r="Q225" t="n">
-        <v>2</v>
-      </c>
-      <c r="R225" t="n">
-        <v>0.4951468781394348</v>
+        <v>0</v>
       </c>
       <c r="S225" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U225" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA225" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR225" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS225" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ225" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS225" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU225" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV225" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW225" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX225" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY225" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ225" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA225" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB225" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC225" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -40111,17 +40119,17 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>CN-AH</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Anhui, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -40155,14 +40163,39 @@
         </is>
       </c>
       <c r="N226" t="n">
-        <v>51</v>
+        <v>0</v>
       </c>
       <c r="O226" t="n">
-        <v>51</v>
-      </c>
-      <c r="S226" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+        <v>0</v>
+      </c>
+      <c r="U226" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W226" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X226" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="Y226" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z226" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA226" t="inlineStr">
@@ -40170,6 +40203,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB226" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC226" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD226" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE226" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF226" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG226" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH226" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI226" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ226" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK226" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary brucellosis notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM226" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN226" t="b">
+        <v>1</v>
+      </c>
       <c r="AO226" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -40177,7 +40268,7 @@
       </c>
       <c r="AP226" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ226" t="inlineStr">
@@ -40187,55 +40278,55 @@
       </c>
       <c r="AS226" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT226" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU226" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV226" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW226" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX226" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY226" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ226" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA226" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB226" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC226" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -40262,17 +40353,17 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>CN-AH</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Anhui, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -40306,170 +40397,84 @@
         </is>
       </c>
       <c r="N227" t="n">
-        <v>51</v>
+        <v>6996</v>
       </c>
       <c r="O227" t="n">
-        <v>51</v>
-      </c>
-      <c r="U227" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
-        </is>
-      </c>
-      <c r="V227" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
-        </is>
-      </c>
-      <c r="W227" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X227" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="Y227" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z227" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
-        </is>
-      </c>
-      <c r="AA227" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB227" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC227" t="inlineStr">
-        <is>
-          <t>country:CN-AH:national</t>
-        </is>
-      </c>
-      <c r="AD227" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE227" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF227" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG227" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH227" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI227" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ227" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK227" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM227" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN227" t="b">
-        <v>1</v>
+        <v>6996</v>
+      </c>
+      <c r="Q227" t="n">
+        <v>2</v>
+      </c>
+      <c r="R227" t="n">
+        <v>0.4951468781394348</v>
+      </c>
+      <c r="S227" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO227" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
-        </is>
-      </c>
-      <c r="AQ227" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS227" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR227" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS227" t="inlineStr"/>
       <c r="AT227" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU227" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV227" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW227" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX227" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY227" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ227" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA227" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB227" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC227" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -40501,12 +40506,12 @@
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN-AH</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Anhui, China</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
@@ -40540,10 +40545,10 @@
         </is>
       </c>
       <c r="N228" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="O228" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="S228" t="inlineStr">
         <is>
@@ -40615,7 +40620,7 @@
       </c>
       <c r="BB228" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
         </is>
       </c>
       <c r="BC228" t="inlineStr">
@@ -40652,12 +40657,12 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN-AH</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Anhui, China</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
@@ -40691,10 +40696,10 @@
         </is>
       </c>
       <c r="N229" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="O229" t="n">
-        <v>11</v>
+        <v>51</v>
       </c>
       <c r="U229" t="inlineStr">
         <is>
@@ -40738,7 +40743,7 @@
       </c>
       <c r="AC229" t="inlineStr">
         <is>
-          <t>country:CN-CQ:national</t>
+          <t>country:CN-AH:national</t>
         </is>
       </c>
       <c r="AD229" t="inlineStr">
@@ -40849,7 +40854,7 @@
       </c>
       <c r="BB229" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.ahlx.gov.cn/Jczwgk/showList/1/125024000/page_1.html</t>
         </is>
       </c>
       <c r="BC229" t="inlineStr">
@@ -40886,12 +40891,12 @@
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
@@ -40925,10 +40930,10 @@
         </is>
       </c>
       <c r="N230" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="O230" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="S230" t="inlineStr">
         <is>
@@ -41000,7 +41005,7 @@
       </c>
       <c r="BB230" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC230" t="inlineStr">
@@ -41037,12 +41042,12 @@
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
@@ -41076,10 +41081,10 @@
         </is>
       </c>
       <c r="N231" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="O231" t="n">
-        <v>70</v>
+        <v>11</v>
       </c>
       <c r="U231" t="inlineStr">
         <is>
@@ -41123,7 +41128,7 @@
       </c>
       <c r="AC231" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD231" t="inlineStr">
@@ -41234,7 +41239,7 @@
       </c>
       <c r="BB231" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC231" t="inlineStr">
@@ -41271,12 +41276,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -41310,10 +41315,10 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="O232" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -41385,7 +41390,7 @@
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
@@ -41422,12 +41427,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -41461,10 +41466,10 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="O233" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="U233" t="inlineStr">
         <is>
@@ -41508,7 +41513,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr">
@@ -41619,7 +41624,7 @@
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
@@ -41656,12 +41661,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -41695,10 +41700,10 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="O234" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -41770,7 +41775,7 @@
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
@@ -41807,12 +41812,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -41846,10 +41851,10 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="O235" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="U235" t="inlineStr">
         <is>
@@ -41893,7 +41898,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr">
@@ -42004,7 +42009,7 @@
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
@@ -42041,12 +42046,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -42080,10 +42085,10 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>385</v>
+        <v>31</v>
       </c>
       <c r="O236" t="n">
-        <v>385</v>
+        <v>31</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -42155,7 +42160,7 @@
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
@@ -42192,12 +42197,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -42231,10 +42236,10 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>385</v>
+        <v>31</v>
       </c>
       <c r="O237" t="n">
-        <v>385</v>
+        <v>31</v>
       </c>
       <c r="U237" t="inlineStr">
         <is>
@@ -42278,7 +42283,7 @@
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD237" t="inlineStr">
@@ -42389,7 +42394,7 @@
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
@@ -42426,12 +42431,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -42465,10 +42470,10 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>40</v>
+        <v>385</v>
       </c>
       <c r="O238" t="n">
-        <v>40</v>
+        <v>385</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -42540,7 +42545,7 @@
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
@@ -42577,12 +42582,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -42616,10 +42621,10 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>40</v>
+        <v>385</v>
       </c>
       <c r="O239" t="n">
-        <v>40</v>
+        <v>385</v>
       </c>
       <c r="U239" t="inlineStr">
         <is>
@@ -42663,7 +42668,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD239" t="inlineStr">
@@ -42774,7 +42779,7 @@
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
@@ -42811,12 +42816,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -42850,10 +42855,10 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O240" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -42925,7 +42930,7 @@
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
@@ -42962,12 +42967,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -43001,10 +43006,10 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O241" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="U241" t="inlineStr">
         <is>
@@ -43048,7 +43053,7 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD241" t="inlineStr">
@@ -43159,7 +43164,7 @@
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
@@ -43196,12 +43201,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -43240,76 +43245,82 @@
       <c r="O242" t="n">
         <v>0</v>
       </c>
-      <c r="R242" t="n">
-        <v>0</v>
-      </c>
       <c r="S242" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP242" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR242" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS242" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ242" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS242" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT242" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU242" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV242" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW242" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX242" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY242" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ242" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA242" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -43336,17 +43347,17 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -43380,29 +43391,104 @@
         </is>
       </c>
       <c r="N243" t="n">
+        <v>0</v>
+      </c>
+      <c r="O243" t="n">
+        <v>0</v>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X243" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z243" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB243" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC243" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD243" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE243" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF243" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG243" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH243" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI243" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ243" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK243" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM243" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN243" t="b">
         <v>1</v>
       </c>
-      <c r="O243" t="n">
-        <v>1</v>
-      </c>
-      <c r="R243" t="n">
-        <v>0.01768975825795506</v>
-      </c>
-      <c r="S243" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U243" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA243" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO243" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -43410,7 +43496,7 @@
       </c>
       <c r="AP243" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ243" t="inlineStr">
@@ -43418,14 +43504,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR243" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS243" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
         </is>
       </c>
       <c r="AT243" t="n">
@@ -43433,47 +43514,47 @@
       </c>
       <c r="AU243" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV243" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW243" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX243" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY243" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ243" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA243" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -43500,17 +43581,17 @@
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -43544,175 +43625,81 @@
         </is>
       </c>
       <c r="N244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O244" t="n">
-        <v>1</v>
-      </c>
-      <c r="U244" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V244" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W244" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X244" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y244" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z244" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA244" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB244" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC244" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD244" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE244" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF244" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG244" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH244" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI244" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ244" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK244" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM244" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN244" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R244" t="n">
+        <v>0</v>
+      </c>
+      <c r="S244" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ244" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR244" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr"/>
       <c r="AT244" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -43744,12 +43731,12 @@
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -43783,13 +43770,13 @@
         </is>
       </c>
       <c r="N245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O245" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R245" t="n">
-        <v>0.01868976085656669</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S245" t="inlineStr">
         <is>
@@ -43798,7 +43785,7 @@
       </c>
       <c r="U245" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AA245" t="inlineStr">
@@ -43828,7 +43815,7 @@
       </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT245" t="n">
@@ -43841,42 +43828,42 @@
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -43908,12 +43895,12 @@
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -43947,29 +43934,29 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O246" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U246" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="V246" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="W246" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X246" t="inlineStr">
         <is>
-          <t>Brucellos</t>
+          <t>Brucellose</t>
         </is>
       </c>
       <c r="Y246" t="inlineStr">
@@ -43994,7 +43981,7 @@
       </c>
       <c r="AC246" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD246" t="inlineStr">
@@ -44029,17 +44016,17 @@
       </c>
       <c r="AJ246" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK246" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -44067,7 +44054,7 @@
       </c>
       <c r="AS246" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT246" t="n">
@@ -44080,42 +44067,42 @@
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44147,12 +44134,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -44177,7 +44164,7 @@
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M247" t="inlineStr">
@@ -44186,81 +44173,100 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R247" t="n">
-        <v>0</v>
+        <v>0.01868976085656669</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP247" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ247" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR247" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS247" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS247" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT247" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU247" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44287,17 +44293,17 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -44322,7 +44328,7 @@
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M248" t="inlineStr">
@@ -44331,81 +44337,175 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O248" t="n">
-        <v>0</v>
-      </c>
-      <c r="R248" t="n">
-        <v>0</v>
-      </c>
-      <c r="S248" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X248" t="inlineStr">
+        <is>
+          <t>Brucellos</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z248" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB248" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC248" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD248" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE248" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF248" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG248" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH248" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI248" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ248" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK248" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM248" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN248" t="b">
+        <v>1</v>
       </c>
       <c r="AO248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP248" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ248" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR248" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS248" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS248" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT248" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU248" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44467,7 +44567,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -44612,7 +44712,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -44621,13 +44721,13 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R250" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S250" t="inlineStr">
         <is>
@@ -44757,7 +44857,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -44902,7 +45002,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -44911,13 +45011,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O252" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R252" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -45047,7 +45147,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -45192,7 +45292,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -45201,13 +45301,13 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O254" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R254" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -45337,7 +45437,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -45452,12 +45552,12 @@
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
@@ -45482,22 +45582,22 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O256" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R256" t="n">
-        <v>0.007345623639039581</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -45530,42 +45630,42 @@
       </c>
       <c r="AV256" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW256" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX256" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY256" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ256" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA256" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB256" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC256" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45597,12 +45697,12 @@
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
@@ -45627,12 +45727,12 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N257" t="n">
@@ -45641,9 +45741,12 @@
       <c r="O257" t="n">
         <v>0</v>
       </c>
+      <c r="R257" t="n">
+        <v>0</v>
+      </c>
       <c r="S257" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO257" t="inlineStr">
@@ -45672,42 +45775,42 @@
       </c>
       <c r="AV257" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW257" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX257" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY257" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ257" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA257" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB257" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC257" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -45739,12 +45842,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45778,14 +45881,17 @@
         </is>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O258" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="R258" t="n">
+        <v>0.007345623639039581</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO258" t="inlineStr">
@@ -45819,12 +45925,12 @@
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
@@ -45839,12 +45945,12 @@
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
@@ -45881,12 +45987,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -45961,7 +46067,7 @@
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
@@ -45981,7 +46087,7 @@
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
@@ -46023,12 +46129,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -46103,7 +46209,7 @@
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
@@ -46123,7 +46229,7 @@
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
@@ -46165,12 +46271,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -46245,7 +46351,7 @@
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
@@ -46265,7 +46371,7 @@
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
@@ -46307,12 +46413,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -46387,7 +46493,7 @@
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
@@ -46407,7 +46513,7 @@
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
@@ -46449,12 +46555,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46529,7 +46635,7 @@
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
@@ -46549,7 +46655,7 @@
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
@@ -46591,12 +46697,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46671,7 +46777,7 @@
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
@@ -46691,7 +46797,7 @@
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
@@ -46733,12 +46839,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46772,20 +46878,14 @@
         </is>
       </c>
       <c r="N265" t="n">
-        <v>6151</v>
+        <v>0</v>
       </c>
       <c r="O265" t="n">
-        <v>6151</v>
-      </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
-      <c r="R265" t="n">
-        <v>0.4353414018633023</v>
+        <v>0</v>
       </c>
       <c r="S265" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO265" t="inlineStr">
@@ -46814,42 +46914,42 @@
       </c>
       <c r="AV265" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY265" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ265" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC265" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -46881,12 +46981,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -46920,17 +47020,14 @@
         </is>
       </c>
       <c r="N266" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O266" t="n">
-        <v>1</v>
-      </c>
-      <c r="R266" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S266" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO266" t="inlineStr">
@@ -46959,42 +47056,42 @@
       </c>
       <c r="AV266" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY266" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ266" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC266" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47026,12 +47123,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -47065,100 +47162,84 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>6151</v>
       </c>
       <c r="O267" t="n">
+        <v>6151</v>
+      </c>
+      <c r="Q267" t="n">
         <v>0</v>
       </c>
       <c r="R267" t="n">
-        <v>0</v>
+        <v>0.4353414018633023</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U267" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA267" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO267" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP267" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ267" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR267" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS267" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS267" t="inlineStr"/>
       <c r="AT267" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU267" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -47185,17 +47266,17 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -47229,175 +47310,81 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O268" t="n">
-        <v>0</v>
-      </c>
-      <c r="U268" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V268" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W268" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X268" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y268" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z268" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA268" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB268" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC268" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD268" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE268" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF268" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG268" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH268" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI268" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ268" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK268" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM268" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN268" t="b">
         <v>1</v>
       </c>
+      <c r="R268" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S268" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP268" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ268" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR268" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS268" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS268" t="inlineStr"/>
       <c r="AT268" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU268" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -47429,12 +47416,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47468,13 +47455,13 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>0.009344880428283346</v>
+        <v>0</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
@@ -47483,7 +47470,7 @@
       </c>
       <c r="U269" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AA269" t="inlineStr">
@@ -47513,7 +47500,7 @@
       </c>
       <c r="AS269" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT269" t="n">
@@ -47526,42 +47513,42 @@
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -47593,12 +47580,12 @@
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47632,29 +47619,29 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O270" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U270" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="V270" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="W270" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X270" t="inlineStr">
         <is>
-          <t>Brucellos</t>
+          <t>Brucellose</t>
         </is>
       </c>
       <c r="Y270" t="inlineStr">
@@ -47679,7 +47666,7 @@
       </c>
       <c r="AC270" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD270" t="inlineStr">
@@ -47714,17 +47701,17 @@
       </c>
       <c r="AJ270" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK270" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM270" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN270" t="b">
@@ -47752,7 +47739,7 @@
       </c>
       <c r="AS270" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT270" t="n">
@@ -47765,42 +47752,42 @@
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -47832,12 +47819,12 @@
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47862,7 +47849,7 @@
       </c>
       <c r="L271" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M271" t="inlineStr">
@@ -47877,75 +47864,94 @@
         <v>1</v>
       </c>
       <c r="R271" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S271" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ271" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR271" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS271" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS271" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT271" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -47972,17 +47978,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -48007,7 +48013,7 @@
       </c>
       <c r="L272" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M272" t="inlineStr">
@@ -48016,81 +48022,175 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O272" t="n">
-        <v>0</v>
-      </c>
-      <c r="R272" t="n">
-        <v>0</v>
-      </c>
-      <c r="S272" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X272" t="inlineStr">
+        <is>
+          <t>Brucellos</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z272" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB272" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC272" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD272" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE272" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF272" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG272" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH272" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI272" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ272" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK272" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM272" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN272" t="b">
+        <v>1</v>
       </c>
       <c r="AO272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ272" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR272" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS272" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS272" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT272" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -48122,12 +48222,12 @@
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -48152,7 +48252,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -48167,7 +48267,7 @@
         <v>1</v>
       </c>
       <c r="R273" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S273" t="inlineStr">
         <is>
@@ -48200,42 +48300,42 @@
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -48297,7 +48397,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -48442,7 +48542,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -48587,7 +48687,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -48732,7 +48832,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -48741,13 +48841,13 @@
         </is>
       </c>
       <c r="N277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O277" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R277" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S277" t="inlineStr">
         <is>
@@ -48877,7 +48977,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -48992,12 +49092,12 @@
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -49022,22 +49122,22 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N279" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O279" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R279" t="n">
-        <v>0</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S279" t="inlineStr">
         <is>
@@ -49070,42 +49170,42 @@
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -49137,12 +49237,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -49167,12 +49267,12 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N280" t="n">
@@ -49215,42 +49315,42 @@
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -49282,12 +49382,12 @@
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -49334,87 +49434,68 @@
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U281" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA281" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO281" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ281" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR281" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS281" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr"/>
       <c r="AT281" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA281" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB281" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC281" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -49441,217 +49522,526 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J282" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L282" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M282" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N282" t="n">
+        <v>0</v>
+      </c>
+      <c r="O282" t="n">
+        <v>0</v>
+      </c>
+      <c r="R282" t="n">
+        <v>0</v>
+      </c>
+      <c r="S282" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO282" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP282" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR282" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr"/>
+      <c r="AT282" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU282" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV282" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ282" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA282" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB282" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC282" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E283" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J283" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L283" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M283" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N283" t="n">
+        <v>0</v>
+      </c>
+      <c r="O283" t="n">
+        <v>0</v>
+      </c>
+      <c r="R283" t="n">
+        <v>0</v>
+      </c>
+      <c r="S283" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO283" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP283" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ283" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR283" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS283" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT283" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU283" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV283" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ283" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA283" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB283" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC283" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E284" t="inlineStr">
+        <is>
           <t>source_series_observation</t>
         </is>
       </c>
-      <c r="F282" t="inlineStr">
+      <c r="F284" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="G282" t="inlineStr">
+      <c r="G284" t="inlineStr">
         <is>
           <t>Norway</t>
         </is>
       </c>
-      <c r="H282" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I282" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J282" t="inlineStr">
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J284" t="inlineStr">
         <is>
           <t>布鲁氏菌病</t>
         </is>
       </c>
-      <c r="K282" t="inlineStr">
+      <c r="K284" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
+      <c r="L284" t="inlineStr">
         <is>
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="M282" t="inlineStr">
+      <c r="M284" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N282" t="n">
-        <v>0</v>
-      </c>
-      <c r="O282" t="n">
-        <v>0</v>
-      </c>
-      <c r="U282" t="inlineStr">
+      <c r="N284" t="n">
+        <v>0</v>
+      </c>
+      <c r="O284" t="n">
+        <v>0</v>
+      </c>
+      <c r="U284" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="V282" t="inlineStr">
+      <c r="V284" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="W282" t="inlineStr">
+      <c r="W284" t="inlineStr">
         <is>
           <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
-      <c r="X282" t="inlineStr">
+      <c r="X284" t="inlineStr">
         <is>
           <t>Brucellose</t>
         </is>
       </c>
-      <c r="Y282" t="inlineStr">
+      <c r="Y284" t="inlineStr">
         <is>
           <t>case_notifications</t>
         </is>
       </c>
-      <c r="Z282" t="inlineStr">
+      <c r="Z284" t="inlineStr">
         <is>
           <t>national_notifiable_disease_registry</t>
         </is>
       </c>
-      <c r="AA282" t="inlineStr">
+      <c r="AA284" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB282" t="inlineStr">
+      <c r="AB284" t="inlineStr">
         <is>
           <t>count</t>
         </is>
       </c>
-      <c r="AC282" t="inlineStr">
+      <c r="AC284" t="inlineStr">
         <is>
           <t>country:NO:national</t>
         </is>
       </c>
-      <c r="AD282" t="inlineStr">
+      <c r="AD284" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE282" t="inlineStr">
+      <c r="AE284" t="inlineStr">
         <is>
           <t>exact</t>
         </is>
       </c>
-      <c r="AF282" t="inlineStr">
+      <c r="AF284" t="inlineStr">
         <is>
           <t>conditional</t>
         </is>
       </c>
-      <c r="AG282" t="inlineStr">
+      <c r="AG284" t="inlineStr">
         <is>
           <t>non_additive</t>
         </is>
       </c>
-      <c r="AH282" t="inlineStr">
+      <c r="AH284" t="inlineStr">
         <is>
           <t>active</t>
         </is>
       </c>
-      <c r="AI282" t="inlineStr">
+      <c r="AI284" t="inlineStr">
         <is>
           <t>missing_is_unknown</t>
         </is>
       </c>
-      <c r="AJ282" t="inlineStr">
+      <c r="AJ284" t="inlineStr">
         <is>
           <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
-      <c r="AK282" t="inlineStr">
+      <c r="AK284" t="inlineStr">
         <is>
           <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
-      <c r="AM282" t="inlineStr">
+      <c r="AM284" t="inlineStr">
         <is>
           <t>provisional; raw; revised</t>
         </is>
       </c>
-      <c r="AN282" t="b">
+      <c r="AN284" t="b">
         <v>1</v>
       </c>
-      <c r="AO282" t="inlineStr">
+      <c r="AO284" t="inlineStr">
         <is>
           <t>series_registry</t>
         </is>
       </c>
-      <c r="AP282" t="inlineStr">
+      <c r="AP284" t="inlineStr">
         <is>
           <t>representative_series</t>
         </is>
       </c>
-      <c r="AQ282" t="inlineStr">
+      <c r="AQ284" t="inlineStr">
         <is>
           <t>parity</t>
         </is>
       </c>
-      <c r="AR282" t="inlineStr">
+      <c r="AR284" t="inlineStr">
         <is>
           <t>non_additive_series_not_rolled_up</t>
         </is>
       </c>
-      <c r="AS282" t="inlineStr">
+      <c r="AS284" t="inlineStr">
         <is>
           <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
-      <c r="AT282" t="n">
+      <c r="AT284" t="n">
         <v>2</v>
       </c>
-      <c r="AU282" t="inlineStr">
+      <c r="AU284" t="inlineStr">
         <is>
           <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
-      <c r="AV282" t="inlineStr">
+      <c r="AV284" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="AW282" t="inlineStr">
+      <c r="AW284" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="AX282" t="inlineStr">
+      <c r="AX284" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="AY282" t="inlineStr">
+      <c r="AY284" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
       </c>
-      <c r="AZ282" t="inlineStr">
+      <c r="AZ284" t="inlineStr">
         <is>
           <t>fhi_msis</t>
         </is>
       </c>
-      <c r="BA282" t="inlineStr">
+      <c r="BA284" t="inlineStr">
         <is>
           <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
-      <c r="BB282" t="inlineStr">
+      <c r="BB284" t="inlineStr">
         <is>
           <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
-      <c r="BC282" t="inlineStr">
+      <c r="BC284" t="inlineStr">
         <is>
           <t>official_json_api</t>
         </is>
@@ -49773,7 +50163,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>199</v>
+        <v>200</v>
       </c>
     </row>
     <row r="10">
@@ -49783,7 +50173,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="11">
@@ -49803,7 +50193,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -50047,6 +50047,151 @@
         </is>
       </c>
     </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E285" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J285" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L285" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N285" t="n">
+        <v>0</v>
+      </c>
+      <c r="O285" t="n">
+        <v>0</v>
+      </c>
+      <c r="R285" t="n">
+        <v>0</v>
+      </c>
+      <c r="S285" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO285" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP285" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR285" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr"/>
+      <c r="AT285" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU285" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV285" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ285" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA285" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB285" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC285" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -50080,7 +50225,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -50163,7 +50308,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>200</v>
+        <v>201</v>
       </c>
     </row>
     <row r="10">
@@ -50173,7 +50318,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -50192,6 +50192,151 @@
         </is>
       </c>
     </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E286" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J286" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L286" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M286" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N286" t="n">
+        <v>1</v>
+      </c>
+      <c r="O286" t="n">
+        <v>1</v>
+      </c>
+      <c r="R286" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S286" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO286" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP286" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR286" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr"/>
+      <c r="AT286" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU286" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV286" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ286" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA286" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB286" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC286" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -50225,7 +50370,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-12</t>
         </is>
       </c>
     </row>
@@ -50308,7 +50453,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>201</v>
+        <v>202</v>
       </c>
     </row>
     <row r="10">
@@ -50318,7 +50463,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="11">
@@ -50370,7 +50515,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49755</v>
+        <v>49756</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -50337,6 +50337,151 @@
         </is>
       </c>
     </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E287" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>0</v>
+      </c>
+      <c r="O287" t="n">
+        <v>0</v>
+      </c>
+      <c r="R287" t="n">
+        <v>0</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR287" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr"/>
+      <c r="AT287" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV287" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA287" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB287" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC287" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -50370,7 +50515,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -50453,7 +50598,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>202</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10">
@@ -50463,7 +50608,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -41276,12 +41276,12 @@
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G232" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H232" t="inlineStr">
@@ -41315,10 +41315,10 @@
         </is>
       </c>
       <c r="N232" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="O232" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="S232" t="inlineStr">
         <is>
@@ -41390,7 +41390,7 @@
       </c>
       <c r="BB232" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC232" t="inlineStr">
@@ -41427,12 +41427,12 @@
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-FJ</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Fujian, China</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
@@ -41466,10 +41466,10 @@
         </is>
       </c>
       <c r="N233" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="O233" t="n">
-        <v>70</v>
+        <v>24</v>
       </c>
       <c r="U233" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
       </c>
       <c r="AC233" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-FJ:national</t>
         </is>
       </c>
       <c r="AD233" t="inlineStr">
@@ -41624,7 +41624,7 @@
       </c>
       <c r="BB233" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.fujian.gov.cn/xxgk/zfxxgkzl/zfxxgkml/ggws/fdcrbyqgb/</t>
         </is>
       </c>
       <c r="BC233" t="inlineStr">
@@ -41661,12 +41661,12 @@
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
@@ -41700,10 +41700,10 @@
         </is>
       </c>
       <c r="N234" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="O234" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="S234" t="inlineStr">
         <is>
@@ -41775,7 +41775,7 @@
       </c>
       <c r="BB234" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC234" t="inlineStr">
@@ -41812,12 +41812,12 @@
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
@@ -41851,10 +41851,10 @@
         </is>
       </c>
       <c r="N235" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="O235" t="n">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="U235" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
       </c>
       <c r="AC235" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD235" t="inlineStr">
@@ -42009,7 +42009,7 @@
       </c>
       <c r="BB235" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC235" t="inlineStr">
@@ -42046,12 +42046,12 @@
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
@@ -42085,10 +42085,10 @@
         </is>
       </c>
       <c r="N236" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="O236" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="S236" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
       </c>
       <c r="BB236" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC236" t="inlineStr">
@@ -42197,12 +42197,12 @@
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
@@ -42236,10 +42236,10 @@
         </is>
       </c>
       <c r="N237" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="O237" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="U237" t="inlineStr">
         <is>
@@ -42283,7 +42283,7 @@
       </c>
       <c r="AC237" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD237" t="inlineStr">
@@ -42394,7 +42394,7 @@
       </c>
       <c r="BB237" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC237" t="inlineStr">
@@ -42431,12 +42431,12 @@
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
@@ -42470,10 +42470,10 @@
         </is>
       </c>
       <c r="N238" t="n">
-        <v>385</v>
+        <v>31</v>
       </c>
       <c r="O238" t="n">
-        <v>385</v>
+        <v>31</v>
       </c>
       <c r="S238" t="inlineStr">
         <is>
@@ -42545,7 +42545,7 @@
       </c>
       <c r="BB238" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC238" t="inlineStr">
@@ -42582,12 +42582,12 @@
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
@@ -42621,10 +42621,10 @@
         </is>
       </c>
       <c r="N239" t="n">
-        <v>385</v>
+        <v>31</v>
       </c>
       <c r="O239" t="n">
-        <v>385</v>
+        <v>31</v>
       </c>
       <c r="U239" t="inlineStr">
         <is>
@@ -42668,7 +42668,7 @@
       </c>
       <c r="AC239" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD239" t="inlineStr">
@@ -42779,7 +42779,7 @@
       </c>
       <c r="BB239" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC239" t="inlineStr">
@@ -42816,12 +42816,12 @@
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
@@ -42855,10 +42855,10 @@
         </is>
       </c>
       <c r="N240" t="n">
-        <v>40</v>
+        <v>385</v>
       </c>
       <c r="O240" t="n">
-        <v>40</v>
+        <v>385</v>
       </c>
       <c r="S240" t="inlineStr">
         <is>
@@ -42930,7 +42930,7 @@
       </c>
       <c r="BB240" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC240" t="inlineStr">
@@ -42967,12 +42967,12 @@
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
@@ -43006,10 +43006,10 @@
         </is>
       </c>
       <c r="N241" t="n">
-        <v>40</v>
+        <v>385</v>
       </c>
       <c r="O241" t="n">
-        <v>40</v>
+        <v>385</v>
       </c>
       <c r="U241" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
       </c>
       <c r="AC241" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD241" t="inlineStr">
@@ -43164,7 +43164,7 @@
       </c>
       <c r="BB241" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC241" t="inlineStr">
@@ -43201,12 +43201,12 @@
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
@@ -43240,10 +43240,10 @@
         </is>
       </c>
       <c r="N242" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O242" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="S242" t="inlineStr">
         <is>
@@ -43315,7 +43315,7 @@
       </c>
       <c r="BB242" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC242" t="inlineStr">
@@ -43352,12 +43352,12 @@
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
@@ -43391,10 +43391,10 @@
         </is>
       </c>
       <c r="N243" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="O243" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="U243" t="inlineStr">
         <is>
@@ -43438,7 +43438,7 @@
       </c>
       <c r="AC243" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD243" t="inlineStr">
@@ -43549,7 +43549,7 @@
       </c>
       <c r="BB243" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC243" t="inlineStr">
@@ -43586,12 +43586,12 @@
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
@@ -43630,76 +43630,82 @@
       <c r="O244" t="n">
         <v>0</v>
       </c>
-      <c r="R244" t="n">
-        <v>0</v>
-      </c>
       <c r="S244" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP244" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR244" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS244" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ244" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS244" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT244" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU244" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV244" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW244" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX244" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY244" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ244" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA244" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB244" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC244" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -43726,17 +43732,17 @@
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
@@ -43770,29 +43776,104 @@
         </is>
       </c>
       <c r="N245" t="n">
+        <v>0</v>
+      </c>
+      <c r="O245" t="n">
+        <v>0</v>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X245" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z245" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB245" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC245" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD245" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE245" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF245" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG245" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH245" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI245" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ245" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK245" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM245" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN245" t="b">
         <v>1</v>
       </c>
-      <c r="O245" t="n">
-        <v>1</v>
-      </c>
-      <c r="R245" t="n">
-        <v>0.01768975825795506</v>
-      </c>
-      <c r="S245" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U245" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA245" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO245" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -43800,7 +43881,7 @@
       </c>
       <c r="AP245" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ245" t="inlineStr">
@@ -43808,14 +43889,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR245" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS245" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
         </is>
       </c>
       <c r="AT245" t="n">
@@ -43823,47 +43899,47 @@
       </c>
       <c r="AU245" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ245" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA245" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB245" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC245" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -43890,17 +43966,17 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
@@ -43934,175 +44010,81 @@
         </is>
       </c>
       <c r="N246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O246" t="n">
-        <v>1</v>
-      </c>
-      <c r="U246" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V246" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W246" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X246" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y246" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z246" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA246" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB246" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC246" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD246" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE246" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF246" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG246" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH246" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI246" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ246" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK246" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM246" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN246" t="b">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="R246" t="n">
+        <v>0</v>
+      </c>
+      <c r="S246" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO246" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP246" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ246" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR246" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS246" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS246" t="inlineStr"/>
       <c r="AT246" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU246" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ246" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA246" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB246" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC246" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -44134,12 +44116,12 @@
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
@@ -44173,13 +44155,13 @@
         </is>
       </c>
       <c r="N247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O247" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R247" t="n">
-        <v>0.01868976085656669</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S247" t="inlineStr">
         <is>
@@ -44188,7 +44170,7 @@
       </c>
       <c r="U247" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AA247" t="inlineStr">
@@ -44218,7 +44200,7 @@
       </c>
       <c r="AS247" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT247" t="n">
@@ -44231,42 +44213,42 @@
       </c>
       <c r="AV247" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW247" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX247" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY247" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ247" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA247" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB247" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC247" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44298,12 +44280,12 @@
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
@@ -44337,29 +44319,29 @@
         </is>
       </c>
       <c r="N248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O248" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U248" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="V248" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="W248" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X248" t="inlineStr">
         <is>
-          <t>Brucellos</t>
+          <t>Brucellose</t>
         </is>
       </c>
       <c r="Y248" t="inlineStr">
@@ -44384,7 +44366,7 @@
       </c>
       <c r="AC248" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD248" t="inlineStr">
@@ -44419,17 +44401,17 @@
       </c>
       <c r="AJ248" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK248" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -44457,7 +44439,7 @@
       </c>
       <c r="AS248" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT248" t="n">
@@ -44470,42 +44452,42 @@
       </c>
       <c r="AV248" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW248" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX248" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY248" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ248" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA248" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB248" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC248" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -44537,12 +44519,12 @@
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
@@ -44567,7 +44549,7 @@
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M249" t="inlineStr">
@@ -44576,81 +44558,100 @@
         </is>
       </c>
       <c r="N249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R249" t="n">
-        <v>0</v>
+        <v>0.01868976085656669</v>
       </c>
       <c r="S249" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP249" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ249" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR249" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS249" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS249" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT249" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU249" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ249" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA249" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB249" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC249" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44677,17 +44678,17 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
@@ -44712,7 +44713,7 @@
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M250" t="inlineStr">
@@ -44721,81 +44722,175 @@
         </is>
       </c>
       <c r="N250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O250" t="n">
-        <v>0</v>
-      </c>
-      <c r="R250" t="n">
-        <v>0</v>
-      </c>
-      <c r="S250" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X250" t="inlineStr">
+        <is>
+          <t>Brucellos</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z250" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB250" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC250" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD250" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE250" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF250" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG250" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH250" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI250" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ250" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK250" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM250" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN250" t="b">
+        <v>1</v>
       </c>
       <c r="AO250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP250" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ250" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR250" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS250" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS250" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT250" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU250" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV250" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW250" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX250" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY250" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ250" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA250" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB250" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC250" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -44857,7 +44952,7 @@
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M251" t="inlineStr">
@@ -45002,7 +45097,7 @@
       </c>
       <c r="L252" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M252" t="inlineStr">
@@ -45011,13 +45106,13 @@
         </is>
       </c>
       <c r="N252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O252" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R252" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0</v>
       </c>
       <c r="S252" t="inlineStr">
         <is>
@@ -45147,7 +45242,7 @@
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M253" t="inlineStr">
@@ -45292,7 +45387,7 @@
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M254" t="inlineStr">
@@ -45301,13 +45396,13 @@
         </is>
       </c>
       <c r="N254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O254" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R254" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S254" t="inlineStr">
         <is>
@@ -45437,7 +45532,7 @@
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M255" t="inlineStr">
@@ -45582,7 +45677,7 @@
       </c>
       <c r="L256" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M256" t="inlineStr">
@@ -45591,13 +45686,13 @@
         </is>
       </c>
       <c r="N256" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O256" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R256" t="n">
-        <v>0.0008595114398308156</v>
+        <v>0</v>
       </c>
       <c r="S256" t="inlineStr">
         <is>
@@ -45727,7 +45822,7 @@
       </c>
       <c r="L257" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M257" t="inlineStr">
@@ -45842,12 +45937,12 @@
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
@@ -45872,22 +45967,22 @@
       </c>
       <c r="L258" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N258" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O258" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R258" t="n">
-        <v>0.007345623639039581</v>
+        <v>0.0008595114398308156</v>
       </c>
       <c r="S258" t="inlineStr">
         <is>
@@ -45920,42 +46015,42 @@
       </c>
       <c r="AV258" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW258" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX258" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY258" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ258" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA258" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB258" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC258" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -45987,12 +46082,12 @@
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
@@ -46017,12 +46112,12 @@
       </c>
       <c r="L259" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N259" t="n">
@@ -46031,9 +46126,12 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
+      <c r="R259" t="n">
+        <v>0</v>
+      </c>
       <c r="S259" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO259" t="inlineStr">
@@ -46062,42 +46160,42 @@
       </c>
       <c r="AV259" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW259" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX259" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY259" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ259" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA259" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB259" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC259" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -46129,12 +46227,12 @@
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
@@ -46168,14 +46266,17 @@
         </is>
       </c>
       <c r="N260" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O260" t="n">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="R260" t="n">
+        <v>0.007345623639039581</v>
       </c>
       <c r="S260" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO260" t="inlineStr">
@@ -46209,12 +46310,12 @@
       </c>
       <c r="AW260" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX260" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY260" t="inlineStr">
@@ -46229,12 +46330,12 @@
       </c>
       <c r="BA260" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB260" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC260" t="inlineStr">
@@ -46271,12 +46372,12 @@
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
@@ -46351,7 +46452,7 @@
       </c>
       <c r="AW261" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX261" t="inlineStr">
@@ -46371,7 +46472,7 @@
       </c>
       <c r="BA261" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB261" t="inlineStr">
@@ -46413,12 +46514,12 @@
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
@@ -46493,7 +46594,7 @@
       </c>
       <c r="AW262" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX262" t="inlineStr">
@@ -46513,7 +46614,7 @@
       </c>
       <c r="BA262" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB262" t="inlineStr">
@@ -46555,12 +46656,12 @@
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
@@ -46635,7 +46736,7 @@
       </c>
       <c r="AW263" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX263" t="inlineStr">
@@ -46655,7 +46756,7 @@
       </c>
       <c r="BA263" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB263" t="inlineStr">
@@ -46697,12 +46798,12 @@
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
@@ -46777,7 +46878,7 @@
       </c>
       <c r="AW264" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX264" t="inlineStr">
@@ -46797,7 +46898,7 @@
       </c>
       <c r="BA264" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB264" t="inlineStr">
@@ -46839,12 +46940,12 @@
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
@@ -46919,7 +47020,7 @@
       </c>
       <c r="AW265" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX265" t="inlineStr">
@@ -46939,7 +47040,7 @@
       </c>
       <c r="BA265" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB265" t="inlineStr">
@@ -46981,12 +47082,12 @@
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
@@ -47061,7 +47162,7 @@
       </c>
       <c r="AW266" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX266" t="inlineStr">
@@ -47081,7 +47182,7 @@
       </c>
       <c r="BA266" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB266" t="inlineStr">
@@ -47123,12 +47224,12 @@
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
@@ -47162,20 +47263,14 @@
         </is>
       </c>
       <c r="N267" t="n">
-        <v>6151</v>
+        <v>0</v>
       </c>
       <c r="O267" t="n">
-        <v>6151</v>
-      </c>
-      <c r="Q267" t="n">
-        <v>0</v>
-      </c>
-      <c r="R267" t="n">
-        <v>0.4353414018633023</v>
+        <v>0</v>
       </c>
       <c r="S267" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO267" t="inlineStr">
@@ -47204,42 +47299,42 @@
       </c>
       <c r="AV267" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW267" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX267" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY267" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ267" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA267" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB267" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC267" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47271,12 +47366,12 @@
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
@@ -47310,17 +47405,14 @@
         </is>
       </c>
       <c r="N268" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O268" t="n">
-        <v>1</v>
-      </c>
-      <c r="R268" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S268" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AO268" t="inlineStr">
@@ -47349,42 +47441,42 @@
       </c>
       <c r="AV268" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW268" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX268" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY268" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ268" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA268" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB268" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC268" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -47416,12 +47508,12 @@
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
@@ -47455,100 +47547,84 @@
         </is>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>6151</v>
       </c>
       <c r="O269" t="n">
+        <v>6151</v>
+      </c>
+      <c r="Q269" t="n">
         <v>0</v>
       </c>
       <c r="R269" t="n">
-        <v>0</v>
+        <v>0.4353414018633023</v>
       </c>
       <c r="S269" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U269" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="AA269" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO269" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP269" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ269" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR269" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS269" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS269" t="inlineStr"/>
       <c r="AT269" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU269" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV269" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW269" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX269" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY269" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ269" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA269" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB269" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC269" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -47575,17 +47651,17 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
@@ -47619,39 +47695,14 @@
         </is>
       </c>
       <c r="N270" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="O270" t="n">
-        <v>0</v>
-      </c>
-      <c r="U270" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V270" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W270" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X270" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y270" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z270" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>9</v>
+      </c>
+      <c r="S270" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA270" t="inlineStr">
@@ -47659,64 +47710,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB270" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC270" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD270" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE270" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF270" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG270" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH270" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI270" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ270" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK270" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM270" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN270" t="b">
-        <v>1</v>
-      </c>
       <c r="AO270" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47724,7 +47717,7 @@
       </c>
       <c r="AP270" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ270" t="inlineStr">
@@ -47732,14 +47725,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR270" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS270" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
         </is>
       </c>
       <c r="AT270" t="n">
@@ -47747,47 +47735,47 @@
       </c>
       <c r="AU270" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV270" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW270" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX270" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY270" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ270" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA270" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB270" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC270" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -47814,17 +47802,17 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
@@ -47858,29 +47846,104 @@
         </is>
       </c>
       <c r="N271" t="n">
+        <v>9</v>
+      </c>
+      <c r="O271" t="n">
+        <v>9</v>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X271" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z271" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB271" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC271" t="inlineStr">
+        <is>
+          <t>country:CN-CQ:national</t>
+        </is>
+      </c>
+      <c r="AD271" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE271" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF271" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG271" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH271" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI271" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ271" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK271" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM271" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN271" t="b">
         <v>1</v>
       </c>
-      <c r="O271" t="n">
-        <v>1</v>
-      </c>
-      <c r="R271" t="n">
-        <v>0.009344880428283346</v>
-      </c>
-      <c r="S271" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U271" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
-        </is>
-      </c>
-      <c r="AA271" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO271" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -47888,7 +47951,7 @@
       </c>
       <c r="AP271" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ271" t="inlineStr">
@@ -47896,14 +47959,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR271" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS271" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
         </is>
       </c>
       <c r="AT271" t="n">
@@ -47911,47 +47969,47 @@
       </c>
       <c r="AU271" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV271" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW271" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX271" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY271" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ271" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA271" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB271" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC271" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -47978,17 +48036,17 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
@@ -48022,39 +48080,14 @@
         </is>
       </c>
       <c r="N272" t="n">
-        <v>1</v>
+        <v>54</v>
       </c>
       <c r="O272" t="n">
-        <v>1</v>
-      </c>
-      <c r="U272" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
-        </is>
-      </c>
-      <c r="V272" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
-        </is>
-      </c>
-      <c r="W272" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X272" t="inlineStr">
-        <is>
-          <t>Brucellos</t>
-        </is>
-      </c>
-      <c r="Y272" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z272" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>54</v>
+      </c>
+      <c r="S272" t="inlineStr">
+        <is>
+          <t>missing_population</t>
         </is>
       </c>
       <c r="AA272" t="inlineStr">
@@ -48062,64 +48095,6 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB272" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC272" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD272" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE272" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF272" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG272" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH272" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI272" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ272" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK272" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM272" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN272" t="b">
-        <v>1</v>
-      </c>
       <c r="AO272" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -48127,7 +48102,7 @@
       </c>
       <c r="AP272" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ272" t="inlineStr">
@@ -48135,14 +48110,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR272" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS272" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
         </is>
       </c>
       <c r="AT272" t="n">
@@ -48150,47 +48120,47 @@
       </c>
       <c r="AU272" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV272" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW272" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX272" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY272" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ272" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA272" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB272" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC272" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -48217,17 +48187,17 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
@@ -48252,7 +48222,7 @@
       </c>
       <c r="L273" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M273" t="inlineStr">
@@ -48261,81 +48231,170 @@
         </is>
       </c>
       <c r="N273" t="n">
+        <v>54</v>
+      </c>
+      <c r="O273" t="n">
+        <v>54</v>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X273" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z273" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB273" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC273" t="inlineStr">
+        <is>
+          <t>country:CN-GD:national</t>
+        </is>
+      </c>
+      <c r="AD273" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE273" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF273" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG273" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH273" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI273" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ273" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK273" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM273" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN273" t="b">
         <v>1</v>
       </c>
-      <c r="O273" t="n">
-        <v>1</v>
-      </c>
-      <c r="R273" t="n">
-        <v>0.0008168084075657662</v>
-      </c>
-      <c r="S273" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP273" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR273" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS273" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ273" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS273" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT273" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU273" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV273" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW273" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX273" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY273" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ273" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA273" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB273" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC273" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -48367,12 +48426,12 @@
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
@@ -48397,7 +48456,7 @@
       </c>
       <c r="L274" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M274" t="inlineStr">
@@ -48406,81 +48465,87 @@
         </is>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O274" t="n">
-        <v>0</v>
-      </c>
-      <c r="R274" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="S274" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO274" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP274" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR274" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS274" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ274" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS274" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT274" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU274" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV274" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW274" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX274" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY274" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ274" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA274" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB274" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC274" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -48507,17 +48572,17 @@
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
@@ -48542,7 +48607,7 @@
       </c>
       <c r="L275" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M275" t="inlineStr">
@@ -48551,81 +48616,170 @@
         </is>
       </c>
       <c r="N275" t="n">
+        <v>29</v>
+      </c>
+      <c r="O275" t="n">
+        <v>29</v>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X275" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z275" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB275" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC275" t="inlineStr">
+        <is>
+          <t>country:CN-HN:national</t>
+        </is>
+      </c>
+      <c r="AD275" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE275" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF275" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG275" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH275" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI275" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ275" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK275" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM275" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN275" t="b">
         <v>1</v>
       </c>
-      <c r="O275" t="n">
-        <v>1</v>
-      </c>
-      <c r="R275" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S275" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO275" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP275" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR275" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS275" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ275" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS275" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT275" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU275" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV275" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW275" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX275" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY275" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ275" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA275" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB275" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC275" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -48657,12 +48811,12 @@
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
@@ -48687,7 +48841,7 @@
       </c>
       <c r="L276" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M276" t="inlineStr">
@@ -48696,81 +48850,87 @@
         </is>
       </c>
       <c r="N276" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O276" t="n">
-        <v>0</v>
-      </c>
-      <c r="R276" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="S276" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO276" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP276" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR276" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS276" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ276" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS276" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT276" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU276" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV276" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW276" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX276" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY276" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ276" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA276" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB276" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC276" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -48797,17 +48957,17 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
@@ -48832,7 +48992,7 @@
       </c>
       <c r="L277" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M277" t="inlineStr">
@@ -48841,81 +49001,170 @@
         </is>
       </c>
       <c r="N277" t="n">
+        <v>30</v>
+      </c>
+      <c r="O277" t="n">
+        <v>30</v>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X277" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z277" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB277" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC277" t="inlineStr">
+        <is>
+          <t>country:CN-JS:national</t>
+        </is>
+      </c>
+      <c r="AD277" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE277" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF277" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG277" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH277" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI277" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ277" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK277" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM277" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN277" t="b">
         <v>1</v>
       </c>
-      <c r="O277" t="n">
-        <v>1</v>
-      </c>
-      <c r="R277" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S277" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP277" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR277" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS277" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ277" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS277" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT277" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU277" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV277" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW277" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX277" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY277" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ277" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA277" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB277" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC277" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -48947,12 +49196,12 @@
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
@@ -48977,7 +49226,7 @@
       </c>
       <c r="L278" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M278" t="inlineStr">
@@ -48986,81 +49235,87 @@
         </is>
       </c>
       <c r="N278" t="n">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="O278" t="n">
-        <v>0</v>
-      </c>
-      <c r="R278" t="n">
-        <v>0</v>
+        <v>272</v>
       </c>
       <c r="S278" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP278" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR278" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS278" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ278" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS278" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT278" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU278" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV278" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW278" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX278" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY278" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ278" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA278" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB278" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC278" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -49087,17 +49342,17 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
@@ -49122,7 +49377,7 @@
       </c>
       <c r="L279" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M279" t="inlineStr">
@@ -49131,81 +49386,170 @@
         </is>
       </c>
       <c r="N279" t="n">
+        <v>272</v>
+      </c>
+      <c r="O279" t="n">
+        <v>272</v>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X279" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z279" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB279" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC279" t="inlineStr">
+        <is>
+          <t>country:CN-LN:national</t>
+        </is>
+      </c>
+      <c r="AD279" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE279" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF279" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG279" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH279" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI279" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ279" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK279" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM279" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN279" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO279" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP279" t="inlineStr">
+        <is>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ279" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS279" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT279" t="n">
         <v>2</v>
       </c>
-      <c r="O279" t="n">
-        <v>2</v>
-      </c>
-      <c r="R279" t="n">
-        <v>0.0005730076265538771</v>
-      </c>
-      <c r="S279" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AO279" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AP279" t="inlineStr">
-        <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR279" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS279" t="inlineStr"/>
-      <c r="AT279" t="n">
-        <v>0</v>
-      </c>
       <c r="AU279" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV279" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW279" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX279" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY279" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ279" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA279" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB279" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC279" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -49237,12 +49581,12 @@
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
@@ -49267,7 +49611,7 @@
       </c>
       <c r="L280" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M280" t="inlineStr">
@@ -49276,81 +49620,87 @@
         </is>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O280" t="n">
-        <v>0</v>
-      </c>
-      <c r="R280" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S280" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO280" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP280" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR280" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS280" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ280" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS280" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT280" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU280" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV280" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW280" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX280" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY280" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ280" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA280" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB280" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC280" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -49377,17 +49727,17 @@
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
@@ -49412,90 +49762,179 @@
       </c>
       <c r="L281" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N281" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="O281" t="n">
-        <v>0</v>
-      </c>
-      <c r="R281" t="n">
-        <v>0</v>
-      </c>
-      <c r="S281" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>38</v>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X281" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z281" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB281" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC281" t="inlineStr">
+        <is>
+          <t>country:CN-SC:national</t>
+        </is>
+      </c>
+      <c r="AD281" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE281" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF281" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG281" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH281" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI281" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ281" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK281" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM281" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN281" t="b">
+        <v>1</v>
       </c>
       <c r="AO281" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP281" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR281" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS281" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ281" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS281" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT281" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU281" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV281" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW281" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX281" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY281" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ281" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA281" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB281" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC281" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -49527,12 +49966,12 @@
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
@@ -49557,90 +49996,96 @@
       </c>
       <c r="L282" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O282" t="n">
-        <v>0</v>
-      </c>
-      <c r="R282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S282" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO282" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP282" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR282" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS282" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ282" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS282" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT282" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU282" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV282" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW282" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX282" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY282" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ282" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA282" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB282" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC282" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -49667,17 +50112,17 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
@@ -49702,31 +50147,48 @@
       </c>
       <c r="L283" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O283" t="n">
-        <v>0</v>
-      </c>
-      <c r="R283" t="n">
-        <v>0</v>
-      </c>
-      <c r="S283" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U283" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X283" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z283" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA283" t="inlineStr">
@@ -49734,6 +50196,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB283" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC283" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD283" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE283" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF283" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG283" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH283" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI283" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ283" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK283" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM283" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN283" t="b">
+        <v>1</v>
+      </c>
       <c r="AO283" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -49741,7 +50261,7 @@
       </c>
       <c r="AP283" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ283" t="inlineStr">
@@ -49749,14 +50269,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR283" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS283" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
         </is>
       </c>
       <c r="AT283" t="n">
@@ -49764,47 +50279,47 @@
       </c>
       <c r="AU283" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV283" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW283" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX283" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY283" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ283" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA283" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB283" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC283" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -49831,17 +50346,17 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
@@ -49866,184 +50381,90 @@
       </c>
       <c r="L284" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O284" t="n">
-        <v>0</v>
-      </c>
-      <c r="U284" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V284" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W284" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X284" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y284" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z284" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA284" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB284" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC284" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD284" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE284" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF284" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG284" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH284" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI284" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ284" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK284" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM284" t="inlineStr">
-        <is>
-          <t>provisional; raw; revised</t>
-        </is>
-      </c>
-      <c r="AN284" t="b">
         <v>1</v>
       </c>
+      <c r="R284" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S284" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AO284" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP284" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ284" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR284" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS284" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS284" t="inlineStr"/>
       <c r="AT284" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU284" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV284" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW284" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX284" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY284" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ284" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA284" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB284" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC284" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -50075,12 +50496,12 @@
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
@@ -50105,12 +50526,12 @@
       </c>
       <c r="L285" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N285" t="n">
@@ -50127,68 +50548,87 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO285" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP285" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ285" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR285" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS285" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS285" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT285" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU285" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV285" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW285" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX285" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY285" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ285" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA285" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB285" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC285" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -50215,17 +50655,17 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
@@ -50250,90 +50690,184 @@
       </c>
       <c r="L286" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N286" t="n">
+        <v>0</v>
+      </c>
+      <c r="O286" t="n">
+        <v>0</v>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X286" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z286" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB286" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC286" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD286" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE286" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF286" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG286" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH286" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI286" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ286" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK286" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM286" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN286" t="b">
         <v>1</v>
       </c>
-      <c r="O286" t="n">
-        <v>1</v>
-      </c>
-      <c r="R286" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S286" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AO286" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP286" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ286" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR286" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS286" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS286" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT286" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU286" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV286" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW286" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX286" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY286" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ286" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA286" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB286" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC286" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -50365,118 +50899,2664 @@
       </c>
       <c r="F287" t="inlineStr">
         <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L287" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N287" t="n">
+        <v>1</v>
+      </c>
+      <c r="O287" t="n">
+        <v>1</v>
+      </c>
+      <c r="R287" t="n">
+        <v>0.009344880428283346</v>
+      </c>
+      <c r="S287" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO287" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP287" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ287" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR287" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS287" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT287" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU287" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV287" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ287" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA287" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB287" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC287" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E288" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>SE</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L288" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N288" t="n">
+        <v>1</v>
+      </c>
+      <c r="O288" t="n">
+        <v>1</v>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X288" t="inlineStr">
+        <is>
+          <t>Brucellos</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z288" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB288" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC288" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD288" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE288" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF288" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG288" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH288" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI288" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ288" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK288" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM288" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN288" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO288" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP288" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ288" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR288" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS288" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="AT288" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU288" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV288" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+      <c r="AZ288" t="inlineStr">
+        <is>
+          <t>fohm_sminet</t>
+        </is>
+      </c>
+      <c r="BA288" t="inlineStr">
+        <is>
+          <t>Sweden Public Health Agency SmiNet</t>
+        </is>
+      </c>
+      <c r="BB288" t="inlineStr">
+        <is>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+        </is>
+      </c>
+      <c r="BC288" t="inlineStr">
+        <is>
+          <t>official_html_csv</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E289" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
           <t>JP</t>
         </is>
       </c>
-      <c r="G287" t="inlineStr">
+      <c r="G289" t="inlineStr">
         <is>
           <t>Japan</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>D032</t>
-        </is>
-      </c>
-      <c r="I287" t="inlineStr">
-        <is>
-          <t>Brucellosis</t>
-        </is>
-      </c>
-      <c r="J287" t="inlineStr">
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J289" t="inlineStr">
         <is>
           <t>布鲁氏菌病</t>
         </is>
       </c>
-      <c r="K287" t="inlineStr">
+      <c r="K289" t="inlineStr">
         <is>
           <t>Bacterial</t>
         </is>
       </c>
-      <c r="L287" t="inlineStr">
+      <c r="L289" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M289" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N289" t="n">
+        <v>1</v>
+      </c>
+      <c r="O289" t="n">
+        <v>1</v>
+      </c>
+      <c r="R289" t="n">
+        <v>0.0008168084075657662</v>
+      </c>
+      <c r="S289" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO289" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP289" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR289" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS289" t="inlineStr"/>
+      <c r="AT289" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU289" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV289" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ289" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA289" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB289" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC289" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E290" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J290" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L290" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M290" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N290" t="n">
+        <v>0</v>
+      </c>
+      <c r="O290" t="n">
+        <v>0</v>
+      </c>
+      <c r="R290" t="n">
+        <v>0</v>
+      </c>
+      <c r="S290" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO290" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP290" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR290" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS290" t="inlineStr"/>
+      <c r="AT290" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU290" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV290" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ290" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA290" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB290" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC290" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E291" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J291" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L291" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="M291" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N291" t="n">
+        <v>1</v>
+      </c>
+      <c r="O291" t="n">
+        <v>1</v>
+      </c>
+      <c r="R291" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S291" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO291" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP291" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR291" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS291" t="inlineStr"/>
+      <c r="AT291" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU291" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV291" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX291" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY291" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ291" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA291" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB291" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC291" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E292" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J292" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L292" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M292" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N292" t="n">
+        <v>0</v>
+      </c>
+      <c r="O292" t="n">
+        <v>0</v>
+      </c>
+      <c r="R292" t="n">
+        <v>0</v>
+      </c>
+      <c r="S292" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO292" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP292" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR292" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS292" t="inlineStr"/>
+      <c r="AT292" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU292" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV292" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW292" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX292" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY292" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ292" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA292" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB292" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC292" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E293" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J293" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L293" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N293" t="n">
+        <v>1</v>
+      </c>
+      <c r="O293" t="n">
+        <v>1</v>
+      </c>
+      <c r="R293" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S293" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO293" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP293" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR293" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS293" t="inlineStr"/>
+      <c r="AT293" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU293" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV293" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW293" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX293" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY293" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ293" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA293" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB293" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC293" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E294" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J294" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L294" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N294" t="n">
+        <v>0</v>
+      </c>
+      <c r="O294" t="n">
+        <v>0</v>
+      </c>
+      <c r="R294" t="n">
+        <v>0</v>
+      </c>
+      <c r="S294" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO294" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP294" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR294" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS294" t="inlineStr"/>
+      <c r="AT294" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU294" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV294" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW294" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX294" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY294" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ294" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA294" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB294" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC294" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E295" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J295" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L295" t="inlineStr">
+        <is>
+          <t>2026-08-29</t>
+        </is>
+      </c>
+      <c r="M295" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N295" t="n">
+        <v>2</v>
+      </c>
+      <c r="O295" t="n">
+        <v>2</v>
+      </c>
+      <c r="R295" t="n">
+        <v>0.0005730076265538771</v>
+      </c>
+      <c r="S295" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO295" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP295" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR295" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS295" t="inlineStr"/>
+      <c r="AT295" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU295" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV295" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW295" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX295" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY295" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ295" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA295" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB295" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC295" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E296" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J296" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L296" t="inlineStr">
+        <is>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="M296" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N296" t="n">
+        <v>0</v>
+      </c>
+      <c r="O296" t="n">
+        <v>0</v>
+      </c>
+      <c r="R296" t="n">
+        <v>0</v>
+      </c>
+      <c r="S296" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO296" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP296" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR296" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS296" t="inlineStr"/>
+      <c r="AT296" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU296" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV296" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW296" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX296" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY296" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ296" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA296" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB296" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC296" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E297" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J297" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L297" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N297" t="n">
+        <v>0</v>
+      </c>
+      <c r="O297" t="n">
+        <v>0</v>
+      </c>
+      <c r="R297" t="n">
+        <v>0</v>
+      </c>
+      <c r="S297" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO297" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP297" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR297" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS297" t="inlineStr"/>
+      <c r="AT297" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU297" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV297" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW297" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX297" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY297" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ297" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA297" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB297" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC297" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E298" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J298" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L298" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M298" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N298" t="n">
+        <v>0</v>
+      </c>
+      <c r="O298" t="n">
+        <v>0</v>
+      </c>
+      <c r="R298" t="n">
+        <v>0</v>
+      </c>
+      <c r="S298" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO298" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP298" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR298" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS298" t="inlineStr"/>
+      <c r="AT298" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU298" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV298" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW298" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX298" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY298" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ298" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA298" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB298" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC298" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E299" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H299" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J299" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L299" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M299" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N299" t="n">
+        <v>0</v>
+      </c>
+      <c r="O299" t="n">
+        <v>0</v>
+      </c>
+      <c r="R299" t="n">
+        <v>0</v>
+      </c>
+      <c r="S299" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U299" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO299" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP299" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ299" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR299" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS299" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT299" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU299" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV299" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW299" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX299" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY299" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ299" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA299" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB299" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC299" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N300" t="n">
+        <v>0</v>
+      </c>
+      <c r="O300" t="n">
+        <v>0</v>
+      </c>
+      <c r="U300" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V300" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W300" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X300" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y300" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z300" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA300" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB300" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC300" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD300" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE300" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF300" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG300" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH300" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI300" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ300" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK300" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM300" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN300" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO300" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP300" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ300" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR300" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS300" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT300" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU300" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV300" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW300" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX300" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY300" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ300" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA300" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB300" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC300" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E301" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N301" t="n">
+        <v>0</v>
+      </c>
+      <c r="O301" t="n">
+        <v>0</v>
+      </c>
+      <c r="R301" t="n">
+        <v>0</v>
+      </c>
+      <c r="S301" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO301" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP301" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR301" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS301" t="inlineStr"/>
+      <c r="AT301" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU301" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV301" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW301" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX301" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY301" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ301" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA301" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB301" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC301" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N302" t="n">
+        <v>1</v>
+      </c>
+      <c r="O302" t="n">
+        <v>1</v>
+      </c>
+      <c r="R302" t="n">
+        <v>0.0002865038132769385</v>
+      </c>
+      <c r="S302" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO302" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP302" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR302" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS302" t="inlineStr"/>
+      <c r="AT302" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU302" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV302" t="inlineStr">
+        <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW302" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX302" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY302" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ302" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA302" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB302" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC302" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E303" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
         <is>
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="M287" t="inlineStr">
+      <c r="M303" t="inlineStr">
         <is>
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N287" t="n">
-        <v>0</v>
-      </c>
-      <c r="O287" t="n">
-        <v>0</v>
-      </c>
-      <c r="R287" t="n">
-        <v>0</v>
-      </c>
-      <c r="S287" t="inlineStr">
+      <c r="N303" t="n">
+        <v>0</v>
+      </c>
+      <c r="O303" t="n">
+        <v>0</v>
+      </c>
+      <c r="R303" t="n">
+        <v>0</v>
+      </c>
+      <c r="S303" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AO287" t="inlineStr">
+      <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AP287" t="inlineStr">
+      <c r="AP303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
         </is>
       </c>
-      <c r="AR287" t="inlineStr">
+      <c r="AR303" t="inlineStr">
         <is>
           <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
-      <c r="AS287" t="inlineStr"/>
-      <c r="AT287" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU287" t="inlineStr">
+      <c r="AS303" t="inlineStr"/>
+      <c r="AT303" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU303" t="inlineStr">
         <is>
           <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
-      <c r="AV287" t="inlineStr">
+      <c r="AV303" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW287" t="inlineStr">
+      <c r="AW303" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX287" t="inlineStr">
+      <c r="AX303" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY287" t="inlineStr">
+      <c r="AY303" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ287" t="inlineStr">
+      <c r="AZ303" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA287" t="inlineStr">
+      <c r="BA303" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB287" t="inlineStr">
+      <c r="BB303" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC287" t="inlineStr">
+      <c r="BC303" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -50598,7 +53678,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="10">
@@ -50608,7 +53688,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>286</v>
+        <v>302</v>
       </c>
     </row>
     <row r="11">
@@ -50628,7 +53708,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>83</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
@@ -50660,7 +53740,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49756</v>
+        <v>50213</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -52501,13 +52501,13 @@
         </is>
       </c>
       <c r="N297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R297" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S297" t="inlineStr">
         <is>
@@ -53559,6 +53559,296 @@
       <c r="BC303" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E304" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N304" t="n">
+        <v>0</v>
+      </c>
+      <c r="O304" t="n">
+        <v>0</v>
+      </c>
+      <c r="R304" t="n">
+        <v>0</v>
+      </c>
+      <c r="S304" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO304" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP304" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR304" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS304" t="inlineStr"/>
+      <c r="AT304" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU304" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV304" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW304" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX304" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY304" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ304" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA304" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB304" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC304" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N305" t="n">
+        <v>0</v>
+      </c>
+      <c r="O305" t="n">
+        <v>0</v>
+      </c>
+      <c r="R305" t="n">
+        <v>0</v>
+      </c>
+      <c r="S305" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO305" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP305" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR305" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS305" t="inlineStr"/>
+      <c r="AT305" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU305" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV305" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW305" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX305" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY305" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ305" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA305" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB305" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC305" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -53595,7 +53885,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -53678,7 +53968,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>211</v>
+        <v>213</v>
       </c>
     </row>
     <row r="10">
@@ -53688,7 +53978,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11">
@@ -53740,7 +54030,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50213</v>
+        <v>50214</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -5312,7 +5312,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN26" t="b">
@@ -11746,7 +11746,7 @@
       </c>
       <c r="AM62" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN62" t="b">
@@ -17647,7 +17647,7 @@
       </c>
       <c r="AM95" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN95" t="b">
@@ -23545,7 +23545,7 @@
       </c>
       <c r="AM128" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN128" t="b">
@@ -29828,7 +29828,7 @@
       </c>
       <c r="AM163" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN163" t="b">
@@ -37016,7 +37016,7 @@
       </c>
       <c r="AM205" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN205" t="b">
@@ -44411,7 +44411,7 @@
       </c>
       <c r="AM248" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN248" t="b">
@@ -50791,7 +50791,7 @@
       </c>
       <c r="AM286" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN286" t="b">
@@ -52791,13 +52791,13 @@
         </is>
       </c>
       <c r="N299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R299" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S299" t="inlineStr">
         <is>
@@ -52955,10 +52955,10 @@
         </is>
       </c>
       <c r="N300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U300" t="inlineStr">
         <is>
@@ -53047,7 +53047,7 @@
       </c>
       <c r="AM300" t="inlineStr">
         <is>
-          <t>provisional; raw; revised</t>
+          <t>raw; revised</t>
         </is>
       </c>
       <c r="AN300" t="b">
@@ -54030,7 +54030,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50214</v>
+        <v>50215</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1057,6 +1067,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1202,6 +1217,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1338,6 +1358,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1483,6 +1508,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1628,6 +1658,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1773,6 +1808,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1918,6 +1958,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2456,6 +2501,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6066,6 +6116,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO32" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6454,7 +6509,7 @@
       </c>
       <c r="AM34" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN34" t="b">
@@ -7020,6 +7075,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO37" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7316,6 +7376,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7612,6 +7677,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO41" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7908,6 +7978,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO43" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8204,6 +8279,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO45" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8352,6 +8432,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8497,6 +8582,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8642,6 +8732,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO48" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8787,6 +8882,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO49" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8932,6 +9032,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO50" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9077,6 +9182,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO51" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9222,6 +9332,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO52" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9367,6 +9482,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -9512,6 +9632,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO54" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -10050,6 +10175,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO57" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -13660,6 +13790,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO76" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -14048,7 +14183,7 @@
       </c>
       <c r="AM78" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN78" t="b">
@@ -14762,6 +14897,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO82" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15058,6 +15198,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO84" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15354,6 +15499,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO86" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15650,6 +15800,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15798,6 +15953,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -15943,6 +16103,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO90" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16088,6 +16253,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16233,6 +16403,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO92" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16378,6 +16553,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO93" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16523,6 +16703,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO94" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16668,6 +16853,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO95" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16813,6 +17003,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO96" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -16958,6 +17153,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO97" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -17496,6 +17696,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -20721,6 +20926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO117" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -21109,7 +21319,7 @@
       </c>
       <c r="AM119" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN119" t="b">
@@ -21823,6 +22033,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO123" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22119,6 +22334,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO125" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22415,6 +22635,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO127" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22711,6 +22936,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA129" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO129" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -22856,6 +23086,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA130" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO130" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23001,6 +23236,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA131" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO131" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23146,6 +23386,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA132" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO132" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23291,6 +23536,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA133" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO133" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23427,6 +23677,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA134" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO134" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23572,6 +23827,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA135" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO135" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23717,6 +23977,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA136" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO136" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -23862,6 +24127,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA137" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO137" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24007,6 +24277,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA138" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO138" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -24545,6 +24820,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA141" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO141" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -27770,6 +28050,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA158" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO158" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -28158,7 +28443,7 @@
       </c>
       <c r="AM160" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN160" t="b">
@@ -28872,6 +29157,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA164" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO164" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29168,6 +29458,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO166" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29464,6 +29759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO168" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29760,6 +30060,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO170" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -29905,6 +30210,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO171" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30050,6 +30360,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO172" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30186,6 +30501,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO173" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30331,6 +30651,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO174" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30476,6 +30801,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO175" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30621,6 +30951,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA176" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO176" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30766,6 +31101,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA177" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO177" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -30911,6 +31251,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA178" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO178" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31056,6 +31401,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA179" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO179" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -31594,6 +31944,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA182" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO182" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35204,6 +35559,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA201" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO201" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -35592,7 +35952,7 @@
       </c>
       <c r="AM203" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN203" t="b">
@@ -36306,6 +36666,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA207" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO207" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36602,6 +36967,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA209" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO209" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -36898,6 +37268,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA211" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO211" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37194,6 +37569,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA213" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO213" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37490,6 +37870,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA215" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO215" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37635,6 +38020,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA216" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO216" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37780,6 +38170,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA217" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO217" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -37925,6 +38320,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA218" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO218" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38070,6 +38470,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA219" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO219" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38215,6 +38620,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA220" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO220" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38360,6 +38770,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA221" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO221" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38505,6 +38920,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA222" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO222" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38641,6 +39061,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA223" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO223" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -38786,6 +39211,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA224" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO224" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -39324,6 +39754,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA227" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO227" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42549,6 +42984,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO244" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -42937,7 +43377,7 @@
       </c>
       <c r="AM246" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN246" t="b">
@@ -43645,6 +44085,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO250" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -43935,6 +44380,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO252" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44225,6 +44675,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO254" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44515,6 +44970,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO256" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44660,6 +45120,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO257" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44805,6 +45270,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO258" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -44950,6 +45420,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO259" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45095,6 +45570,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO260" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45240,6 +45720,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO261" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45385,6 +45870,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO262" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45530,6 +46020,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO263" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45675,6 +46170,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO264" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -45820,6 +46320,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO265" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -46358,6 +46863,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO268" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -49968,6 +50478,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO287" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -50356,7 +50871,7 @@
       </c>
       <c r="AM289" t="inlineStr">
         <is>
-          <t>raw; revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN289" t="b">
@@ -51064,6 +51579,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO293" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51354,6 +51874,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO295" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51644,6 +52169,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO297" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -51934,6 +52464,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA299" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
       <c r="AO299" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52224,6 +52759,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA301" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO301" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52369,6 +52909,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA302" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO302" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52514,6 +53059,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA303" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO303" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52659,6 +53209,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA304" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO304" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52795,6 +53350,11 @@
           <t>missing_population</t>
         </is>
       </c>
+      <c r="AA305" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO305" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -52940,6 +53500,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA306" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO306" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53085,6 +53650,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA307" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO307" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53230,6 +53800,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA308" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO308" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53375,6 +53950,11 @@
           <t>abs_computed</t>
         </is>
       </c>
+      <c r="AA309" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO309" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -53468,12 +54048,12 @@
       </c>
       <c r="F310" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
@@ -53507,84 +54087,92 @@
         </is>
       </c>
       <c r="N310" t="n">
-        <v>6151</v>
+        <v>0</v>
       </c>
       <c r="O310" t="n">
-        <v>6151</v>
-      </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
-      <c r="R310" t="n">
-        <v>0.4353414018633023</v>
+        <v>0</v>
       </c>
       <c r="S310" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="U310" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA310" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO310" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP310" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR310" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS310" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ310" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS310" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU310" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV310" t="inlineStr">
         <is>
-          <t>cdc_weekly</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW310" t="inlineStr">
         <is>
-          <t>China CDC Weekly</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX310" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY310" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ310" t="inlineStr">
         <is>
-          <t>cdc_weekly; nhc; pubmed</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA310" t="inlineStr">
         <is>
-          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB310" t="inlineStr">
         <is>
-          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC310" t="inlineStr">
         <is>
-          <t>web; web; web</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -53611,17 +54199,17 @@
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CA-ON</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>Ontario, Canada</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -53655,14 +54243,39 @@
         </is>
       </c>
       <c r="N311" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O311" t="n">
-        <v>9</v>
-      </c>
-      <c r="S311" t="inlineStr">
-        <is>
-          <t>missing_population</t>
+        <v>0</v>
+      </c>
+      <c r="U311" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V311" t="inlineStr">
+        <is>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W311" t="inlineStr">
+        <is>
+          <t>SRC_CA_ON_PHO_IDTO</t>
+        </is>
+      </c>
+      <c r="X311" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="Y311" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z311" t="inlineStr">
+        <is>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA311" t="inlineStr">
@@ -53670,6 +54283,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB311" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC311" t="inlineStr">
+        <is>
+          <t>country:CA-ON:national</t>
+        </is>
+      </c>
+      <c r="AD311" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE311" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF311" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG311" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH311" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI311" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ311" t="inlineStr">
+        <is>
+          <t>PHO_IDTO_2026_07</t>
+        </is>
+      </c>
+      <c r="AK311" t="inlineStr">
+        <is>
+          <t>PHO IDTO current-year monthly preliminary brucellosis notifications; confirmed cases only under the July 2026 technical notes.</t>
+        </is>
+      </c>
+      <c r="AM311" t="inlineStr">
+        <is>
+          <t>provisional</t>
+        </is>
+      </c>
+      <c r="AN311" t="b">
+        <v>1</v>
+      </c>
       <c r="AO311" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -53677,7 +54348,7 @@
       </c>
       <c r="AP311" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
+          <t>single_series</t>
         </is>
       </c>
       <c r="AQ311" t="inlineStr">
@@ -53687,55 +54358,55 @@
       </c>
       <c r="AS311" t="inlineStr">
         <is>
-          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+          <t>SER_CA_ON_PHO_IDTO_BRUCELLOSIS_MONTHLY</t>
         </is>
       </c>
       <c r="AT311" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU311" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV311" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="AW311" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="AX311" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="AY311" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ311" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>pho_idto_monthly</t>
         </is>
       </c>
       <c r="BA311" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>Public Health Ontario IDTO Monthly</t>
         </is>
       </c>
       <c r="BB311" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://www.publichealthontario.ca/en/data-and-analysis/infectious-disease/reportable-disease-trends-annually</t>
         </is>
       </c>
       <c r="BC311" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -53762,17 +54433,17 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>CN-CQ</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G312" t="inlineStr">
         <is>
-          <t>Chongqing, China</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H312" t="inlineStr">
@@ -53806,39 +54477,20 @@
         </is>
       </c>
       <c r="N312" t="n">
-        <v>9</v>
+        <v>6151</v>
       </c>
       <c r="O312" t="n">
-        <v>9</v>
-      </c>
-      <c r="U312" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
-        </is>
-      </c>
-      <c r="V312" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
-        </is>
-      </c>
-      <c r="W312" t="inlineStr">
-        <is>
-          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
-        </is>
-      </c>
-      <c r="X312" t="inlineStr">
-        <is>
-          <t>布鲁氏菌病</t>
-        </is>
-      </c>
-      <c r="Y312" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z312" t="inlineStr">
-        <is>
-          <t>provincial_statutory_infectious_disease_monthly_report</t>
+        <v>6151</v>
+      </c>
+      <c r="Q312" t="n">
+        <v>0</v>
+      </c>
+      <c r="R312" t="n">
+        <v>0.4353414018633023</v>
+      </c>
+      <c r="S312" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA312" t="inlineStr">
@@ -53846,130 +54498,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB312" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC312" t="inlineStr">
-        <is>
-          <t>country:CN-CQ:national</t>
-        </is>
-      </c>
-      <c r="AD312" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE312" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF312" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG312" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH312" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI312" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ312" t="inlineStr">
-        <is>
-          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
-        </is>
-      </c>
-      <c r="AK312" t="inlineStr">
-        <is>
-          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
-        </is>
-      </c>
-      <c r="AM312" t="inlineStr">
-        <is>
-          <t>raw</t>
-        </is>
-      </c>
-      <c r="AN312" t="b">
-        <v>1</v>
-      </c>
       <c r="AO312" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP312" t="inlineStr">
         <is>
-          <t>priority_overlay</t>
-        </is>
-      </c>
-      <c r="AQ312" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS312" t="inlineStr">
-        <is>
-          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR312" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS312" t="inlineStr"/>
       <c r="AT312" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU312" t="inlineStr">
         <is>
-          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV312" t="inlineStr">
         <is>
-          <t>cn_province_datacenter</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW312" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX312" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY312" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ312" t="inlineStr">
         <is>
-          <t>cn_province_datacenter; cn_province_monthly_report</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA312" t="inlineStr">
         <is>
-          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB312" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC312" t="inlineStr">
         <is>
-          <t>official_datacenter_spreadsheet; official_provincial_report</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -54001,12 +54591,12 @@
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -54040,10 +54630,10 @@
         </is>
       </c>
       <c r="N313" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="O313" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
@@ -54115,7 +54705,7 @@
       </c>
       <c r="BB313" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC313" t="inlineStr">
@@ -54152,12 +54742,12 @@
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>CN-GD</t>
+          <t>CN-CQ</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>Guangdong, China</t>
+          <t>Chongqing, China</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -54191,10 +54781,10 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="O314" t="n">
-        <v>54</v>
+        <v>9</v>
       </c>
       <c r="U314" t="inlineStr">
         <is>
@@ -54238,7 +54828,7 @@
       </c>
       <c r="AC314" t="inlineStr">
         <is>
-          <t>country:CN-GD:national</t>
+          <t>country:CN-CQ:national</t>
         </is>
       </c>
       <c r="AD314" t="inlineStr">
@@ -54349,7 +54939,7 @@
       </c>
       <c r="BB314" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.cq.gov.cn/zwgk_242/wsjklymsxx/ylws_266434/jbfk_266438/yqxx/</t>
         </is>
       </c>
       <c r="BC314" t="inlineStr">
@@ -54386,12 +54976,12 @@
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G315" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H315" t="inlineStr">
@@ -54425,10 +55015,10 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O315" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="S315" t="inlineStr">
         <is>
@@ -54500,7 +55090,7 @@
       </c>
       <c r="BB315" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC315" t="inlineStr">
@@ -54537,12 +55127,12 @@
       </c>
       <c r="F316" t="inlineStr">
         <is>
-          <t>CN-HN</t>
+          <t>CN-GD</t>
         </is>
       </c>
       <c r="G316" t="inlineStr">
         <is>
-          <t>Hunan, China</t>
+          <t>Guangdong, China</t>
         </is>
       </c>
       <c r="H316" t="inlineStr">
@@ -54576,10 +55166,10 @@
         </is>
       </c>
       <c r="N316" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="O316" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="U316" t="inlineStr">
         <is>
@@ -54623,7 +55213,7 @@
       </c>
       <c r="AC316" t="inlineStr">
         <is>
-          <t>country:CN-HN:national</t>
+          <t>country:CN-GD:national</t>
         </is>
       </c>
       <c r="AD316" t="inlineStr">
@@ -54734,7 +55324,7 @@
       </c>
       <c r="BB316" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.gd.gov.cn/zwyw_yqxx/index.html</t>
         </is>
       </c>
       <c r="BC316" t="inlineStr">
@@ -54771,12 +55361,12 @@
       </c>
       <c r="F317" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G317" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H317" t="inlineStr">
@@ -54810,10 +55400,10 @@
         </is>
       </c>
       <c r="N317" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O317" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="S317" t="inlineStr">
         <is>
@@ -54885,7 +55475,7 @@
       </c>
       <c r="BB317" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC317" t="inlineStr">
@@ -54922,12 +55512,12 @@
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>CN-JS</t>
+          <t>CN-HN</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
         <is>
-          <t>Jiangsu, China</t>
+          <t>Hunan, China</t>
         </is>
       </c>
       <c r="H318" t="inlineStr">
@@ -54961,10 +55551,10 @@
         </is>
       </c>
       <c r="N318" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="O318" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="U318" t="inlineStr">
         <is>
@@ -55008,7 +55598,7 @@
       </c>
       <c r="AC318" t="inlineStr">
         <is>
-          <t>country:CN-JS:national</t>
+          <t>country:CN-HN:national</t>
         </is>
       </c>
       <c r="AD318" t="inlineStr">
@@ -55119,7 +55709,7 @@
       </c>
       <c r="BB318" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; http://wjw.hunan.gov.cn/wjw/xxgk/yqsj/</t>
         </is>
       </c>
       <c r="BC318" t="inlineStr">
@@ -55156,12 +55746,12 @@
       </c>
       <c r="F319" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G319" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H319" t="inlineStr">
@@ -55195,10 +55785,10 @@
         </is>
       </c>
       <c r="N319" t="n">
-        <v>272</v>
+        <v>30</v>
       </c>
       <c r="O319" t="n">
-        <v>272</v>
+        <v>30</v>
       </c>
       <c r="S319" t="inlineStr">
         <is>
@@ -55270,7 +55860,7 @@
       </c>
       <c r="BB319" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC319" t="inlineStr">
@@ -55307,12 +55897,12 @@
       </c>
       <c r="F320" t="inlineStr">
         <is>
-          <t>CN-LN</t>
+          <t>CN-JS</t>
         </is>
       </c>
       <c r="G320" t="inlineStr">
         <is>
-          <t>Liaoning, China</t>
+          <t>Jiangsu, China</t>
         </is>
       </c>
       <c r="H320" t="inlineStr">
@@ -55346,10 +55936,10 @@
         </is>
       </c>
       <c r="N320" t="n">
-        <v>272</v>
+        <v>30</v>
       </c>
       <c r="O320" t="n">
-        <v>272</v>
+        <v>30</v>
       </c>
       <c r="U320" t="inlineStr">
         <is>
@@ -55393,7 +55983,7 @@
       </c>
       <c r="AC320" t="inlineStr">
         <is>
-          <t>country:CN-LN:national</t>
+          <t>country:CN-JS:national</t>
         </is>
       </c>
       <c r="AD320" t="inlineStr">
@@ -55504,7 +56094,7 @@
       </c>
       <c r="BB320" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wjw.jiangsu.gov.cn/col/col76875/index.html</t>
         </is>
       </c>
       <c r="BC320" t="inlineStr">
@@ -55541,12 +56131,12 @@
       </c>
       <c r="F321" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G321" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H321" t="inlineStr">
@@ -55580,10 +56170,10 @@
         </is>
       </c>
       <c r="N321" t="n">
-        <v>38</v>
+        <v>272</v>
       </c>
       <c r="O321" t="n">
-        <v>38</v>
+        <v>272</v>
       </c>
       <c r="S321" t="inlineStr">
         <is>
@@ -55655,7 +56245,7 @@
       </c>
       <c r="BB321" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC321" t="inlineStr">
@@ -55692,12 +56282,12 @@
       </c>
       <c r="F322" t="inlineStr">
         <is>
-          <t>CN-SC</t>
+          <t>CN-LN</t>
         </is>
       </c>
       <c r="G322" t="inlineStr">
         <is>
-          <t>Sichuan, China</t>
+          <t>Liaoning, China</t>
         </is>
       </c>
       <c r="H322" t="inlineStr">
@@ -55731,10 +56321,10 @@
         </is>
       </c>
       <c r="N322" t="n">
-        <v>38</v>
+        <v>272</v>
       </c>
       <c r="O322" t="n">
-        <v>38</v>
+        <v>272</v>
       </c>
       <c r="U322" t="inlineStr">
         <is>
@@ -55778,7 +56368,7 @@
       </c>
       <c r="AC322" t="inlineStr">
         <is>
-          <t>country:CN-SC:national</t>
+          <t>country:CN-LN:national</t>
         </is>
       </c>
       <c r="AD322" t="inlineStr">
@@ -55889,7 +56479,7 @@
       </c>
       <c r="BB322" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjk.ln.gov.cn/wsjk/zfxxgk/fdzdgknr/tfggsj/index.shtml</t>
         </is>
       </c>
       <c r="BC322" t="inlineStr">
@@ -55926,12 +56516,12 @@
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H323" t="inlineStr">
@@ -55965,10 +56555,10 @@
         </is>
       </c>
       <c r="N323" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="O323" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="S323" t="inlineStr">
         <is>
@@ -56040,7 +56630,7 @@
       </c>
       <c r="BB323" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC323" t="inlineStr">
@@ -56077,12 +56667,12 @@
       </c>
       <c r="F324" t="inlineStr">
         <is>
-          <t>CN-SH</t>
+          <t>CN-SC</t>
         </is>
       </c>
       <c r="G324" t="inlineStr">
         <is>
-          <t>Shanghai, China</t>
+          <t>Sichuan, China</t>
         </is>
       </c>
       <c r="H324" t="inlineStr">
@@ -56116,10 +56706,10 @@
         </is>
       </c>
       <c r="N324" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="O324" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="U324" t="inlineStr">
         <is>
@@ -56163,7 +56753,7 @@
       </c>
       <c r="AC324" t="inlineStr">
         <is>
-          <t>country:CN-SH:national</t>
+          <t>country:CN-SC:national</t>
         </is>
       </c>
       <c r="AD324" t="inlineStr">
@@ -56274,7 +56864,7 @@
       </c>
       <c r="BB324" t="inlineStr">
         <is>
-          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://www.sccdc.cn/Article/List?ID=132</t>
         </is>
       </c>
       <c r="BC324" t="inlineStr">
@@ -56311,12 +56901,12 @@
       </c>
       <c r="F325" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G325" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H325" t="inlineStr">
@@ -56355,76 +56945,82 @@
       <c r="O325" t="n">
         <v>1</v>
       </c>
-      <c r="R325" t="n">
-        <v>0.001937969923792046</v>
-      </c>
       <c r="S325" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA325" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO325" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP325" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR325" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS325" t="inlineStr"/>
+          <t>priority_overlay</t>
+        </is>
+      </c>
+      <c r="AQ325" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS325" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT325" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU325" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV325" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW325" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX325" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY325" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ325" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA325" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB325" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC325" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -56451,17 +57047,17 @@
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>CN-SH</t>
         </is>
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Shanghai, China</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -56495,22 +57091,39 @@
         </is>
       </c>
       <c r="N326" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O326" t="n">
-        <v>0</v>
-      </c>
-      <c r="R326" t="n">
-        <v>0</v>
-      </c>
-      <c r="S326" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
       </c>
       <c r="U326" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V326" t="inlineStr">
+        <is>
+          <t>SER_CN_PROV_REPORT_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W326" t="inlineStr">
+        <is>
+          <t>SRC_CN_PROV_MONTHLY_REPORT</t>
+        </is>
+      </c>
+      <c r="X326" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="Y326" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z326" t="inlineStr">
+        <is>
+          <t>provincial_statutory_infectious_disease_monthly_report</t>
         </is>
       </c>
       <c r="AA326" t="inlineStr">
@@ -56518,6 +57131,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB326" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC326" t="inlineStr">
+        <is>
+          <t>country:CN-SH:national</t>
+        </is>
+      </c>
+      <c r="AD326" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE326" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF326" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG326" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH326" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI326" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ326" t="inlineStr">
+        <is>
+          <t>CN_PROVINCE_MONTHLY_REPORT_V1</t>
+        </is>
+      </c>
+      <c r="AK326" t="inlineStr">
+        <is>
+          <t>Disease count explicitly published in an official provincial statutory infectious-disease monthly report; absent rows remain unknown and are never zero-filled.</t>
+        </is>
+      </c>
+      <c r="AM326" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN326" t="b">
+        <v>1</v>
+      </c>
       <c r="AO326" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -56525,7 +57196,7 @@
       </c>
       <c r="AP326" t="inlineStr">
         <is>
-          <t>representative_series</t>
+          <t>priority_overlay</t>
         </is>
       </c>
       <c r="AQ326" t="inlineStr">
@@ -56533,14 +57204,9 @@
           <t>parity</t>
         </is>
       </c>
-      <c r="AR326" t="inlineStr">
-        <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
       <c r="AS326" t="inlineStr">
         <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>SER_CN_PROV_DC_BRUCELLOSIS; SER_CN_PROV_REPORT_BRUCELLOSIS</t>
         </is>
       </c>
       <c r="AT326" t="n">
@@ -56548,47 +57214,47 @@
       </c>
       <c r="AU326" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>Retained source series are overlaid per period using their explicit source priority; lower-priority observations remain downloadable.</t>
         </is>
       </c>
       <c r="AV326" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter</t>
         </is>
       </c>
       <c r="AW326" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center</t>
         </is>
       </c>
       <c r="AX326" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp</t>
         </is>
       </c>
       <c r="AY326" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet</t>
         </is>
       </c>
       <c r="AZ326" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>cn_province_datacenter; cn_province_monthly_report</t>
         </is>
       </c>
       <c r="BA326" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Public Health Science Data Center; Provincial statutory infectious disease monthly report</t>
         </is>
       </c>
       <c r="BB326" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.phsciencedata.cn/Share/ky_sjml.jsp; https://wsjkw.sh.gov.cn/yqxx/index.html</t>
         </is>
       </c>
       <c r="BC326" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>official_datacenter_spreadsheet; official_provincial_report</t>
         </is>
       </c>
     </row>
@@ -56615,17 +57281,17 @@
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -56659,39 +57325,17 @@
         </is>
       </c>
       <c r="N327" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O327" t="n">
-        <v>0</v>
-      </c>
-      <c r="U327" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V327" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W327" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X327" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y327" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z327" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>1</v>
+      </c>
+      <c r="R327" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S327" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA327" t="inlineStr">
@@ -56699,135 +57343,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB327" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC327" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD327" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE327" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF327" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG327" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH327" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI327" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ327" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK327" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM327" t="inlineStr">
-        <is>
-          <t>raw; revised</t>
-        </is>
-      </c>
-      <c r="AN327" t="b">
-        <v>1</v>
-      </c>
       <c r="AO327" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP327" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ327" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR327" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS327" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS327" t="inlineStr"/>
       <c r="AT327" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU327" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV327" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW327" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX327" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY327" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ327" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA327" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB327" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC327" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -56859,12 +57436,12 @@
       </c>
       <c r="F328" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G328" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H328" t="inlineStr">
@@ -56898,13 +57475,13 @@
         </is>
       </c>
       <c r="N328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R328" t="n">
-        <v>0.009344880428283346</v>
+        <v>0</v>
       </c>
       <c r="S328" t="inlineStr">
         <is>
@@ -56913,7 +57490,7 @@
       </c>
       <c r="U328" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AA328" t="inlineStr">
@@ -56943,7 +57520,7 @@
       </c>
       <c r="AS328" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT328" t="n">
@@ -56956,42 +57533,42 @@
       </c>
       <c r="AV328" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW328" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX328" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY328" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ328" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA328" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB328" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC328" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -57023,12 +57600,12 @@
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H329" t="inlineStr">
@@ -57062,29 +57639,29 @@
         </is>
       </c>
       <c r="N329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U329" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="V329" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="W329" t="inlineStr">
         <is>
-          <t>SRC_SE_FOHM_SMINET</t>
+          <t>SRC_NO_FHI_MSIS</t>
         </is>
       </c>
       <c r="X329" t="inlineStr">
         <is>
-          <t>Brucellos</t>
+          <t>Brucellose</t>
         </is>
       </c>
       <c r="Y329" t="inlineStr">
@@ -57109,7 +57686,7 @@
       </c>
       <c r="AC329" t="inlineStr">
         <is>
-          <t>country:SE:national</t>
+          <t>country:NO:national</t>
         </is>
       </c>
       <c r="AD329" t="inlineStr">
@@ -57144,17 +57721,17 @@
       </c>
       <c r="AJ329" t="inlineStr">
         <is>
-          <t>SE_FOHM_SMINET_current</t>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
         </is>
       </c>
       <c r="AK329" t="inlineStr">
         <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
         </is>
       </c>
       <c r="AM329" t="inlineStr">
         <is>
-          <t>revised</t>
+          <t>provisional; raw; revised</t>
         </is>
       </c>
       <c r="AN329" t="b">
@@ -57182,7 +57759,7 @@
       </c>
       <c r="AS329" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+          <t>SER_NO_FHI_404_MONTHLY</t>
         </is>
       </c>
       <c r="AT329" t="n">
@@ -57195,42 +57772,42 @@
       </c>
       <c r="AV329" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW329" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX329" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY329" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ329" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA329" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB329" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC329" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -57262,12 +57839,12 @@
       </c>
       <c r="F330" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G330" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H330" t="inlineStr">
@@ -57292,7 +57869,7 @@
       </c>
       <c r="L330" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M330" t="inlineStr">
@@ -57307,75 +57884,94 @@
         <v>1</v>
       </c>
       <c r="R330" t="n">
-        <v>0.0008168084075657662</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S330" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U330" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA330" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO330" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP330" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ330" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR330" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS330" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS330" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT330" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU330" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV330" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW330" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX330" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY330" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ330" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA330" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB330" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC330" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -57402,17 +57998,17 @@
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H331" t="inlineStr">
@@ -57437,7 +58033,7 @@
       </c>
       <c r="L331" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M331" t="inlineStr">
@@ -57446,81 +58042,175 @@
         </is>
       </c>
       <c r="N331" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O331" t="n">
-        <v>0</v>
-      </c>
-      <c r="R331" t="n">
-        <v>0</v>
-      </c>
-      <c r="S331" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U331" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V331" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W331" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X331" t="inlineStr">
+        <is>
+          <t>Brucellos</t>
+        </is>
+      </c>
+      <c r="Y331" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z331" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA331" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB331" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC331" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD331" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE331" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF331" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG331" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH331" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI331" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ331" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK331" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM331" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN331" t="b">
+        <v>1</v>
       </c>
       <c r="AO331" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP331" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ331" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR331" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS331" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS331" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT331" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU331" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV331" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW331" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX331" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY331" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ331" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA331" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB331" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC331" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -57552,12 +58242,12 @@
       </c>
       <c r="F332" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G332" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H332" t="inlineStr">
@@ -57582,7 +58272,7 @@
       </c>
       <c r="L332" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M332" t="inlineStr">
@@ -57597,7 +58287,7 @@
         <v>1</v>
       </c>
       <c r="R332" t="n">
-        <v>0.0002865038132769385</v>
+        <v>0.0008168084075657662</v>
       </c>
       <c r="S332" t="inlineStr">
         <is>
@@ -57630,42 +58320,42 @@
       </c>
       <c r="AV332" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW332" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX332" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY332" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ332" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA332" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB332" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC332" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -57727,7 +58417,7 @@
       </c>
       <c r="L333" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M333" t="inlineStr">
@@ -57872,7 +58562,7 @@
       </c>
       <c r="L334" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="M334" t="inlineStr">
@@ -57892,6 +58582,11 @@
       <c r="S334" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA334" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO334" t="inlineStr">
@@ -58017,7 +58712,7 @@
       </c>
       <c r="L335" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M335" t="inlineStr">
@@ -58162,7 +58857,7 @@
       </c>
       <c r="L336" t="inlineStr">
         <is>
-          <t>2026-08-29</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="M336" t="inlineStr">
@@ -58171,17 +58866,22 @@
         </is>
       </c>
       <c r="N336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O336" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R336" t="n">
-        <v>0.0005730076265538771</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S336" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA336" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO336" t="inlineStr">
@@ -58307,7 +59007,7 @@
       </c>
       <c r="L337" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M337" t="inlineStr">
@@ -58422,12 +59122,12 @@
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H338" t="inlineStr">
@@ -58452,26 +59152,31 @@
       </c>
       <c r="L338" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-29</t>
         </is>
       </c>
       <c r="M338" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N338" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O338" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R338" t="n">
-        <v>0.00367281181951979</v>
+        <v>0.0005730076265538771</v>
       </c>
       <c r="S338" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA338" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO338" t="inlineStr">
@@ -58500,42 +59205,42 @@
       </c>
       <c r="AV338" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api</t>
         </is>
       </c>
       <c r="AW338" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS</t>
         </is>
       </c>
       <c r="AX338" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
         </is>
       </c>
       <c r="AY338" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api</t>
         </is>
       </c>
       <c r="AZ338" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>nndss_api; nhss_hiv</t>
         </is>
       </c>
       <c r="BA338" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
         </is>
       </c>
       <c r="BB338" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
         </is>
       </c>
       <c r="BC338" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>api; api</t>
         </is>
       </c>
     </row>
@@ -58567,12 +59272,12 @@
       </c>
       <c r="F339" t="inlineStr">
         <is>
-          <t>AU-ACT</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G339" t="inlineStr">
         <is>
-          <t>Australian Capital Territory, Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H339" t="inlineStr">
@@ -58597,12 +59302,12 @@
       </c>
       <c r="L339" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N339" t="n">
@@ -58616,7 +59321,7 @@
       </c>
       <c r="S339" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AO339" t="inlineStr">
@@ -58645,42 +59350,42 @@
       </c>
       <c r="AV339" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW339" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX339" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY339" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ339" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA339" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Australian Capital Territory</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB339" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC339" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -58712,12 +59417,12 @@
       </c>
       <c r="F340" t="inlineStr">
         <is>
-          <t>AU-NSW</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G340" t="inlineStr">
         <is>
-          <t>New South Wales, Australia</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H340" t="inlineStr">
@@ -58751,17 +59456,22 @@
         </is>
       </c>
       <c r="N340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R340" t="n">
-        <v>0</v>
+        <v>0.00367281181951979</v>
       </c>
       <c r="S340" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA340" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO340" t="inlineStr">
@@ -58795,12 +59505,12 @@
       </c>
       <c r="AW340" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX340" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY340" t="inlineStr">
@@ -58815,12 +59525,12 @@
       </c>
       <c r="BA340" t="inlineStr">
         <is>
-          <t>Australia NINDSS — New South Wales</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB340" t="inlineStr">
         <is>
-          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC340" t="inlineStr">
@@ -58857,12 +59567,12 @@
       </c>
       <c r="F341" t="inlineStr">
         <is>
-          <t>AU-NT</t>
+          <t>AU-ACT</t>
         </is>
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>Northern Territory, Australia</t>
+          <t>Australian Capital Territory, Australia</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -58907,6 +59617,11 @@
       <c r="S341" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA341" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO341" t="inlineStr">
@@ -58940,7 +59655,7 @@
       </c>
       <c r="AW341" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="AX341" t="inlineStr">
@@ -58960,7 +59675,7 @@
       </c>
       <c r="BA341" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Northern Territory</t>
+          <t>Australia NINDSS — Australian Capital Territory</t>
         </is>
       </c>
       <c r="BB341" t="inlineStr">
@@ -59002,12 +59717,12 @@
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>AU-QLD</t>
+          <t>AU-NSW</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>Queensland, Australia</t>
+          <t>New South Wales, Australia</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -59040,9 +59755,23 @@
           <t>2026-09</t>
         </is>
       </c>
+      <c r="N342" t="n">
+        <v>0</v>
+      </c>
+      <c r="O342" t="n">
+        <v>0</v>
+      </c>
+      <c r="R342" t="n">
+        <v>0</v>
+      </c>
       <c r="S342" t="inlineStr">
         <is>
-          <t>missing_population</t>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA342" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO342" t="inlineStr">
@@ -59076,7 +59805,7 @@
       </c>
       <c r="AW342" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="AX342" t="inlineStr">
@@ -59096,7 +59825,7 @@
       </c>
       <c r="BA342" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Queensland</t>
+          <t>Australia NINDSS — New South Wales</t>
         </is>
       </c>
       <c r="BB342" t="inlineStr">
@@ -59138,12 +59867,12 @@
       </c>
       <c r="F343" t="inlineStr">
         <is>
-          <t>AU-SA</t>
+          <t>AU-NT</t>
         </is>
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>South Australia, Australia</t>
+          <t>Northern Territory, Australia</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
@@ -59188,6 +59917,11 @@
       <c r="S343" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA343" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO343" t="inlineStr">
@@ -59221,7 +59955,7 @@
       </c>
       <c r="AW343" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="AX343" t="inlineStr">
@@ -59241,7 +59975,7 @@
       </c>
       <c r="BA343" t="inlineStr">
         <is>
-          <t>Australia NINDSS — South Australia</t>
+          <t>Australia NINDSS — Northern Territory</t>
         </is>
       </c>
       <c r="BB343" t="inlineStr">
@@ -59283,12 +60017,12 @@
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>AU-TAS</t>
+          <t>AU-QLD</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>Tasmania, Australia</t>
+          <t>Queensland, Australia</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -59321,18 +60055,14 @@
           <t>2026-09</t>
         </is>
       </c>
-      <c r="N344" t="n">
-        <v>0</v>
-      </c>
-      <c r="O344" t="n">
-        <v>0</v>
-      </c>
-      <c r="R344" t="n">
-        <v>0</v>
-      </c>
       <c r="S344" t="inlineStr">
         <is>
-          <t>abs_computed</t>
+          <t>missing_population</t>
+        </is>
+      </c>
+      <c r="AA344" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO344" t="inlineStr">
@@ -59366,7 +60096,7 @@
       </c>
       <c r="AW344" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="AX344" t="inlineStr">
@@ -59386,7 +60116,7 @@
       </c>
       <c r="BA344" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Tasmania</t>
+          <t>Australia NINDSS — Queensland</t>
         </is>
       </c>
       <c r="BB344" t="inlineStr">
@@ -59428,12 +60158,12 @@
       </c>
       <c r="F345" t="inlineStr">
         <is>
-          <t>AU-VIC</t>
+          <t>AU-SA</t>
         </is>
       </c>
       <c r="G345" t="inlineStr">
         <is>
-          <t>Victoria, Australia</t>
+          <t>South Australia, Australia</t>
         </is>
       </c>
       <c r="H345" t="inlineStr">
@@ -59478,6 +60208,11 @@
       <c r="S345" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA345" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO345" t="inlineStr">
@@ -59511,7 +60246,7 @@
       </c>
       <c r="AW345" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="AX345" t="inlineStr">
@@ -59531,7 +60266,7 @@
       </c>
       <c r="BA345" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Victoria</t>
+          <t>Australia NINDSS — South Australia</t>
         </is>
       </c>
       <c r="BB345" t="inlineStr">
@@ -59573,12 +60308,12 @@
       </c>
       <c r="F346" t="inlineStr">
         <is>
-          <t>AU-WA</t>
+          <t>AU-TAS</t>
         </is>
       </c>
       <c r="G346" t="inlineStr">
         <is>
-          <t>Western Australia, Australia</t>
+          <t>Tasmania, Australia</t>
         </is>
       </c>
       <c r="H346" t="inlineStr">
@@ -59623,6 +60358,11 @@
       <c r="S346" t="inlineStr">
         <is>
           <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA346" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO346" t="inlineStr">
@@ -59656,7 +60396,7 @@
       </c>
       <c r="AW346" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="AX346" t="inlineStr">
@@ -59676,7 +60416,7 @@
       </c>
       <c r="BA346" t="inlineStr">
         <is>
-          <t>Australia NINDSS — Western Australia</t>
+          <t>Australia NINDSS — Tasmania</t>
         </is>
       </c>
       <c r="BB346" t="inlineStr">
@@ -59718,12 +60458,12 @@
       </c>
       <c r="F347" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>AU-VIC</t>
         </is>
       </c>
       <c r="G347" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Victoria, Australia</t>
         </is>
       </c>
       <c r="H347" t="inlineStr">
@@ -59767,7 +60507,12 @@
       </c>
       <c r="S347" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
+          <t>abs_computed</t>
+        </is>
+      </c>
+      <c r="AA347" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO347" t="inlineStr">
@@ -59796,42 +60541,42 @@
       </c>
       <c r="AV347" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW347" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="AX347" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY347" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ347" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA347" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Australia NINDSS — Victoria</t>
         </is>
       </c>
       <c r="BB347" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC347" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -59863,12 +60608,12 @@
       </c>
       <c r="F348" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>AU-WA</t>
         </is>
       </c>
       <c r="G348" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>Western Australia, Australia</t>
         </is>
       </c>
       <c r="H348" t="inlineStr">
@@ -59902,22 +60647,17 @@
         </is>
       </c>
       <c r="N348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R348" t="n">
-        <v>0.01768975825795506</v>
+        <v>0</v>
       </c>
       <c r="S348" t="inlineStr">
         <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="U348" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
+          <t>abs_computed</t>
         </is>
       </c>
       <c r="AA348" t="inlineStr">
@@ -59927,75 +60667,66 @@
       </c>
       <c r="AO348" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP348" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ348" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR348" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS348" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS348" t="inlineStr"/>
       <c r="AT348" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU348" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV348" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW348" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="AX348" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="AY348" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ348" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA348" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Australia NINDSS — Western Australia</t>
         </is>
       </c>
       <c r="BB348" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.cdc.gov.au/resources/apps-and-tools/nndss-data-visualisation-tool</t>
         </is>
       </c>
       <c r="BC348" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -60022,17 +60753,17 @@
       </c>
       <c r="E349" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F349" t="inlineStr">
         <is>
-          <t>NO</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G349" t="inlineStr">
         <is>
-          <t>Norway</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H349" t="inlineStr">
@@ -60066,39 +60797,17 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O349" t="n">
-        <v>1</v>
-      </c>
-      <c r="U349" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="V349" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
-      <c r="W349" t="inlineStr">
-        <is>
-          <t>SRC_NO_FHI_MSIS</t>
-        </is>
-      </c>
-      <c r="X349" t="inlineStr">
-        <is>
-          <t>Brucellose</t>
-        </is>
-      </c>
-      <c r="Y349" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z349" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
+        <v>0</v>
+      </c>
+      <c r="R349" t="n">
+        <v>0</v>
+      </c>
+      <c r="S349" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA349" t="inlineStr">
@@ -60106,135 +60815,68 @@
           <t>monthly</t>
         </is>
       </c>
-      <c r="AB349" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC349" t="inlineStr">
-        <is>
-          <t>country:NO:national</t>
-        </is>
-      </c>
-      <c r="AD349" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE349" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF349" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG349" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH349" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI349" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ349" t="inlineStr">
-        <is>
-          <t>NO_FHI_MSIS_diagnosis_monthly</t>
-        </is>
-      </c>
-      <c r="AK349" t="inlineStr">
-        <is>
-          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
-        </is>
-      </c>
-      <c r="AM349" t="inlineStr">
-        <is>
-          <t>raw; revised</t>
-        </is>
-      </c>
-      <c r="AN349" t="b">
-        <v>1</v>
-      </c>
       <c r="AO349" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP349" t="inlineStr">
         <is>
-          <t>representative_series</t>
-        </is>
-      </c>
-      <c r="AQ349" t="inlineStr">
-        <is>
-          <t>parity</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AR349" t="inlineStr">
         <is>
-          <t>non_additive_series_not_rolled_up</t>
-        </is>
-      </c>
-      <c r="AS349" t="inlineStr">
-        <is>
-          <t>SER_NO_FHI_404_MONTHLY</t>
-        </is>
-      </c>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS349" t="inlineStr"/>
       <c r="AT349" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU349" t="inlineStr">
         <is>
-          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV349" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW349" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX349" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY349" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ349" t="inlineStr">
         <is>
-          <t>fhi_msis</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA349" t="inlineStr">
         <is>
-          <t>Norway FHI MSIS Statistics Bank</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB349" t="inlineStr">
         <is>
-          <t>https://allvis.fhi.no/msis</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC349" t="inlineStr">
         <is>
-          <t>official_json_api</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -60266,12 +60908,12 @@
       </c>
       <c r="F350" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G350" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H350" t="inlineStr">
@@ -60296,7 +60938,7 @@
       </c>
       <c r="L350" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M350" t="inlineStr">
@@ -60305,81 +60947,100 @@
         </is>
       </c>
       <c r="N350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R350" t="n">
-        <v>0</v>
+        <v>0.01768975825795506</v>
       </c>
       <c r="S350" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U350" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA350" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO350" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP350" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ350" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR350" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS350" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS350" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT350" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU350" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV350" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW350" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX350" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY350" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ350" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA350" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB350" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC350" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -60406,17 +61067,17 @@
       </c>
       <c r="E351" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F351" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>NO</t>
         </is>
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Norway</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -60441,7 +61102,7 @@
       </c>
       <c r="L351" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M351" t="inlineStr">
@@ -60455,76 +61116,170 @@
       <c r="O351" t="n">
         <v>1</v>
       </c>
-      <c r="R351" t="n">
-        <v>0.0002865038132769385</v>
-      </c>
-      <c r="S351" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+      <c r="U351" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V351" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W351" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X351" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y351" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z351" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA351" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB351" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC351" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD351" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE351" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF351" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG351" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH351" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI351" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ351" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK351" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM351" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN351" t="b">
+        <v>1</v>
       </c>
       <c r="AO351" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP351" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ351" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR351" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS351" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS351" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
       <c r="AT351" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU351" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV351" t="inlineStr">
         <is>
-          <t>nndss_api</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="AW351" t="inlineStr">
         <is>
-          <t>US CDC NNDSS</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="AX351" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="AY351" t="inlineStr">
         <is>
-          <t>api</t>
+          <t>official_json_api</t>
         </is>
       </c>
       <c r="AZ351" t="inlineStr">
         <is>
-          <t>nndss_api; nhss_hiv</t>
+          <t>fhi_msis</t>
         </is>
       </c>
       <c r="BA351" t="inlineStr">
         <is>
-          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+          <t>Norway FHI MSIS Statistics Bank</t>
         </is>
       </c>
       <c r="BB351" t="inlineStr">
         <is>
-          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+          <t>https://allvis.fhi.no/msis</t>
         </is>
       </c>
       <c r="BC351" t="inlineStr">
         <is>
-          <t>api; api</t>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -60556,12 +61311,12 @@
       </c>
       <c r="F352" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -60586,7 +61341,7 @@
       </c>
       <c r="L352" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M352" t="inlineStr">
@@ -60595,81 +61350,100 @@
         </is>
       </c>
       <c r="N352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R352" t="n">
-        <v>0</v>
+        <v>0.009344880428283346</v>
       </c>
       <c r="S352" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U352" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="AA352" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO352" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP352" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ352" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR352" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS352" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS352" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT352" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU352" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV352" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW352" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX352" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY352" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ352" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA352" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB352" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC352" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -60696,17 +61470,17 @@
       </c>
       <c r="E353" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F353" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G353" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H353" t="inlineStr">
@@ -60731,7 +61505,7 @@
       </c>
       <c r="L353" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="M353" t="inlineStr">
@@ -60740,81 +61514,175 @@
         </is>
       </c>
       <c r="N353" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O353" t="n">
-        <v>0</v>
-      </c>
-      <c r="R353" t="n">
-        <v>0</v>
-      </c>
-      <c r="S353" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="U353" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="V353" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
+      <c r="W353" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X353" t="inlineStr">
+        <is>
+          <t>Brucellos</t>
+        </is>
+      </c>
+      <c r="Y353" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z353" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA353" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB353" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC353" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD353" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE353" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF353" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG353" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH353" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI353" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ353" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK353" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM353" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN353" t="b">
+        <v>1</v>
       </c>
       <c r="AO353" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP353" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ353" t="inlineStr">
+        <is>
+          <t>parity</t>
         </is>
       </c>
       <c r="AR353" t="inlineStr">
         <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS353" t="inlineStr"/>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS353" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_BRUCELLOSIS</t>
+        </is>
+      </c>
       <c r="AT353" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU353" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
         </is>
       </c>
       <c r="AV353" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW353" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX353" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY353" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ353" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA353" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB353" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC353" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -60876,7 +61744,7 @@
       </c>
       <c r="L354" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="M354" t="inlineStr">
@@ -60991,12 +61859,12 @@
       </c>
       <c r="F355" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>US</t>
         </is>
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -61021,26 +61889,31 @@
       </c>
       <c r="L355" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-12</t>
         </is>
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O355" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R355" t="n">
-        <v>0</v>
+        <v>0.0002865038132769385</v>
       </c>
       <c r="S355" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA355" t="inlineStr">
+        <is>
+          <t>weekly</t>
         </is>
       </c>
       <c r="AO355" t="inlineStr">
@@ -61069,42 +61942,1030 @@
       </c>
       <c r="AV355" t="inlineStr">
         <is>
+          <t>nndss_api</t>
+        </is>
+      </c>
+      <c r="AW355" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS</t>
+        </is>
+      </c>
+      <c r="AX355" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS</t>
+        </is>
+      </c>
+      <c r="AY355" t="inlineStr">
+        <is>
+          <t>api</t>
+        </is>
+      </c>
+      <c r="AZ355" t="inlineStr">
+        <is>
+          <t>nndss_api; nhss_hiv</t>
+        </is>
+      </c>
+      <c r="BA355" t="inlineStr">
+        <is>
+          <t>US CDC NNDSS; US CDC NHSS HIV</t>
+        </is>
+      </c>
+      <c r="BB355" t="inlineStr">
+        <is>
+          <t>https://data.cdc.gov/browse?category=NNDSS; https://www.cdc.gov/hiv-data/nhss/</t>
+        </is>
+      </c>
+      <c r="BC355" t="inlineStr">
+        <is>
+          <t>api; api</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D356" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E356" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F356" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H356" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J356" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K356" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L356" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M356" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N356" t="n">
+        <v>0</v>
+      </c>
+      <c r="O356" t="n">
+        <v>0</v>
+      </c>
+      <c r="R356" t="n">
+        <v>0</v>
+      </c>
+      <c r="S356" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO356" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP356" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR356" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS356" t="inlineStr"/>
+      <c r="AT356" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU356" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV356" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW356" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX356" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY356" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ356" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA356" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB356" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC356" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D357" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E357" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F357" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H357" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I357" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J357" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K357" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L357" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M357" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N357" t="n">
+        <v>0</v>
+      </c>
+      <c r="O357" t="n">
+        <v>0</v>
+      </c>
+      <c r="R357" t="n">
+        <v>0</v>
+      </c>
+      <c r="S357" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO357" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP357" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR357" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS357" t="inlineStr"/>
+      <c r="AT357" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU357" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV357" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW357" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX357" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY357" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ357" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA357" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB357" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC357" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D358" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E358" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F358" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H358" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I358" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J358" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K358" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L358" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="M358" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N358" t="n">
+        <v>0</v>
+      </c>
+      <c r="O358" t="n">
+        <v>0</v>
+      </c>
+      <c r="R358" t="n">
+        <v>0</v>
+      </c>
+      <c r="S358" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO358" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP358" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR358" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS358" t="inlineStr"/>
+      <c r="AT358" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU358" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV358" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW358" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX358" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY358" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ358" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA358" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB358" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC358" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D359" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E359" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F359" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H359" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I359" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J359" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K359" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L359" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M359" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N359" t="n">
+        <v>0</v>
+      </c>
+      <c r="O359" t="n">
+        <v>0</v>
+      </c>
+      <c r="R359" t="n">
+        <v>0</v>
+      </c>
+      <c r="S359" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA359" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO359" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP359" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR359" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS359" t="inlineStr"/>
+      <c r="AT359" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU359" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV359" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW355" t="inlineStr">
+      <c r="AW359" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX355" t="inlineStr">
+      <c r="AX359" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY355" t="inlineStr">
+      <c r="AY359" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ355" t="inlineStr">
+      <c r="AZ359" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA355" t="inlineStr">
+      <c r="BA359" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB355" t="inlineStr">
+      <c r="BB359" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC355" t="inlineStr">
+      <c r="BC359" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D360" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E360" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F360" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H360" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I360" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J360" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K360" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L360" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M360" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N360" t="n">
+        <v>0</v>
+      </c>
+      <c r="O360" t="n">
+        <v>0</v>
+      </c>
+      <c r="R360" t="n">
+        <v>0</v>
+      </c>
+      <c r="S360" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="U360" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AA360" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AO360" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP360" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ360" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR360" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS360" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT360" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU360" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV360" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW360" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX360" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY360" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ360" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA360" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB360" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC360" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D361" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E361" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F361" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>Norway</t>
+        </is>
+      </c>
+      <c r="H361" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J361" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K361" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L361" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M361" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N361" t="n">
+        <v>0</v>
+      </c>
+      <c r="O361" t="n">
+        <v>0</v>
+      </c>
+      <c r="U361" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="V361" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="W361" t="inlineStr">
+        <is>
+          <t>SRC_NO_FHI_MSIS</t>
+        </is>
+      </c>
+      <c r="X361" t="inlineStr">
+        <is>
+          <t>Brucellose</t>
+        </is>
+      </c>
+      <c r="Y361" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z361" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA361" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB361" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC361" t="inlineStr">
+        <is>
+          <t>country:NO:national</t>
+        </is>
+      </c>
+      <c r="AD361" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE361" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF361" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG361" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH361" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI361" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ361" t="inlineStr">
+        <is>
+          <t>NO_FHI_MSIS_diagnosis_monthly</t>
+        </is>
+      </c>
+      <c r="AK361" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS national monthly diagnosis series; FHI MSIS diagnosis mapping.</t>
+        </is>
+      </c>
+      <c r="AM361" t="inlineStr">
+        <is>
+          <t>provisional; raw; revised</t>
+        </is>
+      </c>
+      <c r="AN361" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO361" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP361" t="inlineStr">
+        <is>
+          <t>representative_series</t>
+        </is>
+      </c>
+      <c r="AQ361" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AR361" t="inlineStr">
+        <is>
+          <t>non_additive_series_not_rolled_up</t>
+        </is>
+      </c>
+      <c r="AS361" t="inlineStr">
+        <is>
+          <t>SER_NO_FHI_404_MONTHLY</t>
+        </is>
+      </c>
+      <c r="AT361" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU361" t="inlineStr">
+        <is>
+          <t>Multiple registered series are not declared safely additive. The compatibility curve uses one representative series; inspect source_series for every retained definition.</t>
+        </is>
+      </c>
+      <c r="AV361" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="AW361" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="AX361" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="AY361" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
+        </is>
+      </c>
+      <c r="AZ361" t="inlineStr">
+        <is>
+          <t>fhi_msis</t>
+        </is>
+      </c>
+      <c r="BA361" t="inlineStr">
+        <is>
+          <t>Norway FHI MSIS Statistics Bank</t>
+        </is>
+      </c>
+      <c r="BB361" t="inlineStr">
+        <is>
+          <t>https://allvis.fhi.no/msis</t>
+        </is>
+      </c>
+      <c r="BC361" t="inlineStr">
+        <is>
+          <t>official_json_api</t>
         </is>
       </c>
     </row>
@@ -61224,7 +63085,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>263</v>
+        <v>266</v>
       </c>
     </row>
     <row r="10">
@@ -61234,7 +63095,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>354</v>
+        <v>360</v>
       </c>
     </row>
     <row r="11">
@@ -61254,7 +63115,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>91</v>
+        <v>94</v>
       </c>
     </row>
     <row r="13">
@@ -61286,7 +63147,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50215</v>
+        <v>50216</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -60797,13 +60797,13 @@
         </is>
       </c>
       <c r="N349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R349" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S349" t="inlineStr">
         <is>
@@ -62966,6 +62966,151 @@
       <c r="BC361" t="inlineStr">
         <is>
           <t>official_json_api</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>brucellosis</t>
+        </is>
+      </c>
+      <c r="D362" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="E362" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F362" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H362" t="inlineStr">
+        <is>
+          <t>D032</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>Brucellosis</t>
+        </is>
+      </c>
+      <c r="J362" t="inlineStr">
+        <is>
+          <t>布鲁氏菌病</t>
+        </is>
+      </c>
+      <c r="K362" t="inlineStr">
+        <is>
+          <t>Bacterial</t>
+        </is>
+      </c>
+      <c r="L362" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M362" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N362" t="n">
+        <v>0</v>
+      </c>
+      <c r="O362" t="n">
+        <v>0</v>
+      </c>
+      <c r="R362" t="n">
+        <v>0</v>
+      </c>
+      <c r="S362" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO362" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP362" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR362" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS362" t="inlineStr"/>
+      <c r="AT362" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU362" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV362" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW362" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX362" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY362" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ362" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA362" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB362" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC362" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -63002,7 +63147,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -63085,7 +63230,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="10">
@@ -63095,7 +63240,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="11">
@@ -63147,7 +63292,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50216</v>
+        <v>50217</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d032/2026-2029.xlsx
+++ b/diseases/d032/2026-2029.xlsx
@@ -15488,9 +15488,6 @@
       <c r="O86" t="n">
         <v>1</v>
       </c>
-      <c r="Q86" t="n">
-        <v>0</v>
-      </c>
       <c r="R86" t="n">
         <v>0.0002865038132769385</v>
       </c>
@@ -37256,9 +37253,6 @@
       </c>
       <c r="O211" t="n">
         <v>2</v>
-      </c>
-      <c r="Q211" t="n">
-        <v>0</v>
       </c>
       <c r="R211" t="n">
         <v>0.0005730076265538771</v>
